--- a/data/merged/2026-09-28/MERGED_JP_Wet-Dry-Floor-Washer_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_JP_Wet-Dry-Floor-Washer_2026-09-28.xlsx
@@ -6299,13 +6299,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6393,7 +6393,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6437,7 +6437,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7042,50 +7042,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Product 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId43" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7411,7 +7367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR44"/>
+  <dimension ref="A1:BR43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -13716,52 +13672,52 @@
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>B0HHN61KPZ</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>品牌: Dyson | 特殊功能: 无绳 | 推荐表面: 硬地板、地毯、被褥、车内 | 电源: 电池供电 | 随附部件: Fluffy Optic™清洁头</t>
+          <t>品牌: dreame | 特殊功能: 大功率, 干湿两用, 无绳, 自動推進 | 筛选类型: 墨盒 | 推荐表面: 所有楼面 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) Dyson V12s Detect Slim Submarine 无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
+          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量水箱 静音设计 高速电机</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>[制造商保修激活] 注册产品后,制造商保修将有效 2 年。 请搜索"戴森产品保修注册",并从戴森官方网站进行产品注册。
-本产品设定了UpCare延长保修服务1年的延长保修。 关于延长保修服务的适用条件,请参阅购买时的保修内容。
-【延长保修证发行】购买本产品后将发出延长保修证书。 在发行保修卡时,我们将向您发送"延长保修受理邮件",请按照邮件中的说明确认客户的延长保修卡。 此外,纸的保修书不随产品一起包装。
-【无法收到邮件的情况】如果客户的邮件接收设定中没有收到延长保修受理邮件,请搜索"UpCare",并从UpCare官方网站确认延长保修卡。
-[延长保修支持范围] 即使在一般制造商保修期(2 年)结束后,自然故障将免费维修和更换长达 1 年。 ※请注意,由于跌落或沾水导致的故障和消耗品劣化不在范围内。</t>
+          <t>【4WAY无线吸尘器套装】多功能类型，可在一台设备中切换使用手持吸尘器、床上用吸尘器、便携吸尘器和水拖式清洁器。 无论是地板、地毯、沙发、楼梯等，家中的污垢都可以交由这一台DREAME吸尘器来处理。
+【能到达墙壁的刷子设计】通过Dreame独特的刷毛结构,能彻底清洁到墙壁间约5mm的缝隙。 连以往难以清洁到的房间角落和家具周围也能清洁干净。
+【自动自清洁功能】清扫后，只需将其放回充电底座并按下按钮。 刷头双向高速旋转，有效去除粘附的污垢和毛发。 无需保养即可随时保持清洁。
+[用水擦拭后55°C温风自动干燥]擦拭后刷子约30分钟即可自动干燥。 抑制霉菌和异味的产生，下次使用时也能愉快地开始。
+【根据污垢自动调整吸力】先进的污垢检测系统，根据污垢的数量和种类自动控制吸力。 适合任何场合的功率有效清洁。</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>B0HHN61KPZ</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
@@ -13775,11 +13731,13 @@
         </is>
       </c>
       <c r="O27" s="13">
-        <v>10436</v>
-      </c>
-      <c r="P27" s="13"/>
+        <v>137815</v>
+      </c>
+      <c r="P27" s="13">
+        <v>2289</v>
+      </c>
       <c r="Q27" s="14">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R27" s="15" t="inlineStr">
         <is>
@@ -13788,15 +13746,17 @@
       </c>
       <c r="S27" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T27" s="13">
-        <v>3</v>
-      </c>
-      <c r="U27" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="U27" s="14">
+        <v>0.06</v>
+      </c>
       <c r="V27" s="13">
-        <v>179997</v>
+        <v>171600</v>
       </c>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
@@ -13804,29 +13764,37 @@
         <v>1</v>
       </c>
       <c r="Z27" s="13">
-        <v>59999</v>
+        <v>42900</v>
       </c>
       <c r="AA27" s="2"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="2"/>
-      <c r="AD27" s="17"/>
-      <c r="AE27" s="13"/>
-      <c r="AF27" s="18"/>
+      <c r="AD27" s="17">
+        <v>44</v>
+      </c>
+      <c r="AE27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="18">
+        <v>3.7</v>
+      </c>
       <c r="AG27" s="19">
         <v>0</v>
       </c>
-      <c r="AH27" s="13"/>
+      <c r="AH27" s="13">
+        <v>1100</v>
+      </c>
       <c r="AI27" s="14">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AJ27"/>
       <c r="AK27" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="AL27" s="17">
-        <v>25</v>
+        <v>1043</v>
       </c>
       <c r="AM27" s="11" t="inlineStr">
         <is>
@@ -13836,13 +13804,15 @@
       <c r="AN27" s="11"/>
       <c r="AO27" s="11"/>
       <c r="AP27" s="2"/>
-      <c r="AQ27" s="17"/>
+      <c r="AQ27" s="17">
+        <v>9</v>
+      </c>
       <c r="AR27" s="17">
         <v>1</v>
       </c>
       <c r="AS27" s="12" t="inlineStr">
         <is>
-          <t>ダイソン公式ストア</t>
+          <t>Dreame公式ストア</t>
         </is>
       </c>
       <c r="AT27" s="11" t="inlineStr">
@@ -13852,17 +13822,17 @@
       </c>
       <c r="AU27" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV27" s="12" t="inlineStr">
         <is>
-          <t>千代田区麹町 東京都 1020083 JP</t>
+          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
         </is>
       </c>
       <c r="AW27" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
         </is>
       </c>
       <c r="AX27" s="11"/>
@@ -13870,30 +13840,62 @@
       <c r="AZ27" s="11"/>
       <c r="BA27" s="11"/>
       <c r="BB27" s="11"/>
-      <c r="BC27" s="11"/>
-      <c r="BD27" s="11"/>
+      <c r="BC27" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD27" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE27" s="11"/>
-      <c r="BF27" s="11"/>
+      <c r="BF27" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG27" s="11"/>
       <c r="BH27" s="12"/>
       <c r="BI27" s="20"/>
       <c r="BJ27" s="20" t="inlineStr">
         <is>
-          <t>3.2 千克</t>
+          <t>5.13 千克</t>
         </is>
       </c>
       <c r="BK27" s="20"/>
       <c r="BL27" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+          <t>27.5長さ x 27.8幅 x 110.5高さ cm</t>
         </is>
       </c>
       <c r="BM27" s="20"/>
-      <c r="BN27" s="20"/>
-      <c r="BO27" s="20"/>
-      <c r="BP27" s="20"/>
-      <c r="BQ27" s="20"/>
-      <c r="BR27" s="11"/>
+      <c r="BN27" s="20" t="inlineStr">
+        <is>
+          <t>13 kg</t>
+        </is>
+      </c>
+      <c r="BO27" s="20" t="inlineStr">
+        <is>
+          <t>13.00 kg</t>
+        </is>
+      </c>
+      <c r="BP27" s="20" t="inlineStr">
+        <is>
+          <t>75 x 38 x 35 cm</t>
+        </is>
+      </c>
+      <c r="BQ27" s="20" t="inlineStr">
+        <is>
+          <t>75.00 x 38.00 x 35.00 cm</t>
+        </is>
+      </c>
+      <c r="BR27" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
@@ -13902,52 +13904,48 @@
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B08XLW562G</t>
         </is>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>品牌: dreame | 特殊功能: 大功率, 干湿两用, 无绳, 自動推進 | 筛选类型: 墨盒 | 推荐表面: 所有楼面 | 电源: 电池供电</t>
+          <t>品牌: 不明 | 特殊功能: 干湿两用 | 推荐表面: 家具装饰品 | 电源: 电池供电 | 是否无绳？: 是</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量水箱 静音设计 高速电机</t>
+          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>【4WAY无线吸尘器套装】多功能类型，可在一台设备中切换使用手持吸尘器、床上用吸尘器、便携吸尘器和水拖式清洁器。 无论是地板、地毯、沙发、楼梯等，家中的污垢都可以交由这一台DREAME吸尘器来处理。
-【能到达墙壁的刷子设计】通过Dreame独特的刷毛结构,能彻底清洁到墙壁间约5mm的缝隙。 连以往难以清洁到的房间角落和家具周围也能清洁干净。
-【自动自清洁功能】清扫后，只需将其放回充电底座并按下按钮。 刷头双向高速旋转，有效去除粘附的污垢和毛发。 无需保养即可随时保持清洁。
-[用水擦拭后55°C温风自动干燥]擦拭后刷子约30分钟即可自动干燥。 抑制霉菌和异味的产生，下次使用时也能愉快地开始。
-【根据污垢自动调整吸力】先进的污垢检测系统，根据污垢的数量和种类自动控制吸力。 适合任何场合的功率有效清洁。</t>
+          <t>乾湿両用</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B08XLW562G</t>
         </is>
       </c>
       <c r="M28" s="12" t="inlineStr">
@@ -13961,13 +13959,13 @@
         </is>
       </c>
       <c r="O28" s="13">
-        <v>137815</v>
+        <v>39624</v>
       </c>
       <c r="P28" s="13">
-        <v>2289</v>
+        <v>-54113</v>
       </c>
       <c r="Q28" s="14">
-        <v>0.02</v>
+        <v>-2.77</v>
       </c>
       <c r="R28" s="15" t="inlineStr">
         <is>
@@ -13976,17 +13974,15 @@
       </c>
       <c r="S28" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T28" s="13">
-        <v>4</v>
-      </c>
-      <c r="U28" s="14">
-        <v>0.06</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U28" s="14"/>
       <c r="V28" s="13">
-        <v>171600</v>
+        <v>135000</v>
       </c>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
@@ -13994,37 +13990,37 @@
         <v>1</v>
       </c>
       <c r="Z28" s="13">
-        <v>42900</v>
+        <v>4500</v>
       </c>
       <c r="AA28" s="2"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="17">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="AE28" s="13">
         <v>0</v>
       </c>
       <c r="AF28" s="18">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AG28" s="19">
         <v>0</v>
       </c>
       <c r="AH28" s="13">
-        <v>1100</v>
+        <v>472</v>
       </c>
       <c r="AI28" s="14">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AJ28"/>
       <c r="AK28" s="11" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2021-06-13</t>
         </is>
       </c>
       <c r="AL28" s="17">
-        <v>1043</v>
+        <v>1933</v>
       </c>
       <c r="AM28" s="11" t="inlineStr">
         <is>
@@ -14035,14 +14031,14 @@
       <c r="AO28" s="11"/>
       <c r="AP28" s="2"/>
       <c r="AQ28" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AR28" s="17">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS28" s="12" t="inlineStr">
         <is>
-          <t>Dreame公式ストア</t>
+          <t>Abeショップ関西</t>
         </is>
       </c>
       <c r="AT28" s="11" t="inlineStr">
@@ -14052,17 +14048,17 @@
       </c>
       <c r="AU28" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV28" s="12" t="inlineStr">
         <is>
-          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
+          <t>桜井市 奈良県 6330112 JP</t>
         </is>
       </c>
       <c r="AW28" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V</t>
         </is>
       </c>
       <c r="AX28" s="11"/>
@@ -14070,60 +14066,56 @@
       <c r="AZ28" s="11"/>
       <c r="BA28" s="11"/>
       <c r="BB28" s="11"/>
-      <c r="BC28" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD28" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC28" s="11"/>
+      <c r="BD28" s="11"/>
       <c r="BE28" s="11"/>
-      <c r="BF28" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF28" s="11"/>
       <c r="BG28" s="11"/>
       <c r="BH28" s="12"/>
       <c r="BI28" s="20"/>
       <c r="BJ28" s="20" t="inlineStr">
         <is>
-          <t>5.13 千克</t>
-        </is>
-      </c>
-      <c r="BK28" s="20"/>
+          <t>1 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK28" s="20" t="inlineStr">
+        <is>
+          <t>1,000.00 g</t>
+        </is>
+      </c>
       <c r="BL28" s="20" t="inlineStr">
         <is>
-          <t>27.5長さ x 27.8幅 x 110.5高さ cm</t>
-        </is>
-      </c>
-      <c r="BM28" s="20"/>
+          <t>30 x 10 x 10 cm</t>
+        </is>
+      </c>
+      <c r="BM28" s="20" t="inlineStr">
+        <is>
+          <t>30.00 x 10.00 x 10.00 cm</t>
+        </is>
+      </c>
       <c r="BN28" s="20" t="inlineStr">
         <is>
-          <t>13 kg</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="BO28" s="20" t="inlineStr">
         <is>
-          <t>13.00 kg</t>
+          <t>1,000.00 g</t>
         </is>
       </c>
       <c r="BP28" s="20" t="inlineStr">
         <is>
-          <t>75 x 38 x 35 cm</t>
+          <t>43.8 x 13.9 x 11.7 cm</t>
         </is>
       </c>
       <c r="BQ28" s="20" t="inlineStr">
         <is>
-          <t>75.00 x 38.00 x 35.00 cm</t>
+          <t>43.80 x 13.90 x 11.70 cm</t>
         </is>
       </c>
       <c r="BR28" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -14134,257 +14126,35 @@
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>B08XLW562G</t>
-        </is>
-      </c>
-      <c r="D29" s="12"/>
+          <t>B0GXDDCQ3M</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>颜色: 白</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>品牌: 不明 | 特殊功能: 干湿两用 | 推荐表面: 家具装饰品 | 电源: 电池供电 | 是否无绳？: 是</t>
+          <t>品牌: YTE PRO | 颜色: 白 | 商品重量: 4 千克 | 商品尺寸: 19深度 x 41宽度 x 30高度 厘米 | 电源: 有线电动</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>YTE PRO</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
+          <t>[2026新上市 400W 强力吸力] 支持60°C热水 自动清洗 去污 干湿两用 吸尘器 布清洗机 沙发/地毯/布制品/车内/毛绒玩具/羽绒外套/缝隙 移动方便 便于保养 日本国内PSE&amp;METI认证</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>乾湿両用</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>B08XLW562G</t>
-        </is>
-      </c>
-      <c r="M29" s="12" t="inlineStr">
-        <is>
-          <t>家装及园艺:电动工具:商用干湿两用吸尘器</t>
-        </is>
-      </c>
-      <c r="N29" s="12" t="inlineStr">
-        <is>
-          <t>家装及园艺</t>
-        </is>
-      </c>
-      <c r="O29" s="13">
-        <v>39624</v>
-      </c>
-      <c r="P29" s="13">
-        <v>-54113</v>
-      </c>
-      <c r="Q29" s="14">
-        <v>-2.77</v>
-      </c>
-      <c r="R29" s="15" t="inlineStr">
-        <is>
-          <t>商用干湿两用吸尘器</t>
-        </is>
-      </c>
-      <c r="S29" s="16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="T29" s="13">
-        <v>30</v>
-      </c>
-      <c r="U29" s="14"/>
-      <c r="V29" s="13">
-        <v>135000</v>
-      </c>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="13">
-        <v>4500</v>
-      </c>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="2"/>
-      <c r="AD29" s="17">
-        <v>3</v>
-      </c>
-      <c r="AE29" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="18">
-        <v>2.7</v>
-      </c>
-      <c r="AG29" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="13">
-        <v>472</v>
-      </c>
-      <c r="AI29" s="14">
-        <v>0.75</v>
-      </c>
-      <c r="AJ29"/>
-      <c r="AK29" s="11" t="inlineStr">
-        <is>
-          <t>2021-06-13</t>
-        </is>
-      </c>
-      <c r="AL29" s="17">
-        <v>1933</v>
-      </c>
-      <c r="AM29" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN29" s="11"/>
-      <c r="AO29" s="11"/>
-      <c r="AP29" s="2"/>
-      <c r="AQ29" s="17">
-        <v>3</v>
-      </c>
-      <c r="AR29" s="17">
-        <v>8</v>
-      </c>
-      <c r="AS29" s="12" t="inlineStr">
-        <is>
-          <t>Abeショップ関西</t>
-        </is>
-      </c>
-      <c r="AT29" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU29" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV29" s="12" t="inlineStr">
-        <is>
-          <t>桜井市 奈良県 6330112 JP</t>
-        </is>
-      </c>
-      <c r="AW29" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V</t>
-        </is>
-      </c>
-      <c r="AX29" s="11"/>
-      <c r="AY29" s="11"/>
-      <c r="AZ29" s="11"/>
-      <c r="BA29" s="11"/>
-      <c r="BB29" s="11"/>
-      <c r="BC29" s="11"/>
-      <c r="BD29" s="11"/>
-      <c r="BE29" s="11"/>
-      <c r="BF29" s="11"/>
-      <c r="BG29" s="11"/>
-      <c r="BH29" s="12"/>
-      <c r="BI29" s="20"/>
-      <c r="BJ29" s="20" t="inlineStr">
-        <is>
-          <t>1 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK29" s="20" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BL29" s="20" t="inlineStr">
-        <is>
-          <t>30 x 10 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BM29" s="20" t="inlineStr">
-        <is>
-          <t>30.00 x 10.00 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BN29" s="20" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
-      </c>
-      <c r="BO29" s="20" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BP29" s="20" t="inlineStr">
-        <is>
-          <t>43.8 x 13.9 x 11.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ29" s="20" t="inlineStr">
-        <is>
-          <t>43.80 x 13.90 x 11.70 cm</t>
-        </is>
-      </c>
-      <c r="BR29" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>29</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>B0GXDDCQ3M</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>颜色: 白</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>品牌: YTE PRO | 颜色: 白 | 商品重量: 4 千克 | 商品尺寸: 19深度 x 41宽度 x 30高度 厘米 | 电源: 有线电动</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>YTE PRO</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>[2026新上市 400W 强力吸力] 支持60°C热水 自动清洗 去污 干湿两用 吸尘器 布清洗机 沙发/地毯/布制品/车内/毛绒玩具/羽绒外套/缝隙 移动方便 便于保养 日本国内PSE&amp;METI认证</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>【2026年新上市! [YTE PRO 地毯清洁剂] YTE PRO 地毯清洁剂可将水喷到脏区域并漂浮污垢,同时吸收污垢和水! 干湿两用节水,地毯等布制品的清洗革命方便。 刷子由高性能尼龙材料制成,柔软不伤布制品。
 [强大的清洁力] 配备400W高性能电机,可以彻底清洁顽固的污垢和异味。 具备高压喷射和12Kpa的强大吸力,可以轻松清洁深度4.5厘米的布制品。 适用于沙发和地毯上积累的灰尘、汗渍、咖啡、酱油、淤青污渍、儿童食物溢出物、宠物吐痰/粗糙/足迹等。
@@ -14394,19 +14164,246 @@
 YTE PRO 地毯清洁剂,非常适合作为搬家或新婚朋友的礼物。 本公司产品已取得PSE认证,已完成METI注册,请放心使用。 另外,购买后1年内初期不良及正常使用范围内发生的故障、破损或其他问题时,可进行退款・退货・换货。</t>
         </is>
       </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>B0GXZR4TNN</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>家装及园艺:电动工具:商用干湿两用吸尘器</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>家装及园艺</t>
+        </is>
+      </c>
+      <c r="O29" s="13">
+        <v>2087</v>
+      </c>
+      <c r="P29" s="13">
+        <v>102044</v>
+      </c>
+      <c r="Q29" s="14">
+        <v>0.92</v>
+      </c>
+      <c r="R29" s="15" t="inlineStr">
+        <is>
+          <t>商用干湿两用吸尘器</t>
+        </is>
+      </c>
+      <c r="S29" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T29" s="13">
+        <v>9</v>
+      </c>
+      <c r="U29" s="14"/>
+      <c r="V29" s="13">
+        <v>80991</v>
+      </c>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="13">
+        <v>8999</v>
+      </c>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="17">
+        <v>30</v>
+      </c>
+      <c r="AE29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="18">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="13">
+        <v>532</v>
+      </c>
+      <c r="AI29" s="14">
+        <v>0.79</v>
+      </c>
+      <c r="AJ29"/>
+      <c r="AK29" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AL29" s="17">
+        <v>16</v>
+      </c>
+      <c r="AM29" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN29" s="11"/>
+      <c r="AO29" s="11"/>
+      <c r="AP29" s="2"/>
+      <c r="AQ29" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR29" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS29" s="12" t="inlineStr">
+        <is>
+          <t>HighWin LLC</t>
+        </is>
+      </c>
+      <c r="AT29" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU29" s="11" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV29" s="12" t="inlineStr">
+        <is>
+          <t>HONG KONG HONG KONG 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW29" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V</t>
+        </is>
+      </c>
+      <c r="AX29" s="11"/>
+      <c r="AY29" s="11"/>
+      <c r="AZ29" s="11"/>
+      <c r="BA29" s="11"/>
+      <c r="BB29" s="11"/>
+      <c r="BC29" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD29" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE29" s="11"/>
+      <c r="BF29" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG29" s="11"/>
+      <c r="BH29" s="12"/>
+      <c r="BI29" s="20"/>
+      <c r="BJ29" s="20" t="inlineStr">
+        <is>
+          <t>4 千克</t>
+        </is>
+      </c>
+      <c r="BK29" s="20"/>
+      <c r="BL29" s="20" t="inlineStr">
+        <is>
+          <t>19 x 41 x 30 cm</t>
+        </is>
+      </c>
+      <c r="BM29" s="20" t="inlineStr">
+        <is>
+          <t>19.00 x 41.00 x 30.00 cm</t>
+        </is>
+      </c>
+      <c r="BN29" s="20" t="inlineStr">
+        <is>
+          <t>4.1 kg</t>
+        </is>
+      </c>
+      <c r="BO29" s="20" t="inlineStr">
+        <is>
+          <t>4.10 kg</t>
+        </is>
+      </c>
+      <c r="BP29" s="20" t="inlineStr">
+        <is>
+          <t>41 x 30 x 19 cm</t>
+        </is>
+      </c>
+      <c r="BQ29" s="20" t="inlineStr">
+        <is>
+          <t>41.00 x 30.00 x 19.00 cm</t>
+        </is>
+      </c>
+      <c r="BR29" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>B0H6DZMNPV</t>
+        </is>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>dreame</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>【2026年新上市! 】Dreame推出超薄多功能手持吸尘器。 适用于城市型住宅的紧凑设计,具备多种功能。 超薄多功能手持吸尘器T16,9.85厘米超薄机身和180°全平设计,能够轻松进入家具下方,发挥强大的吸力。 此外,轻量机身可以快速旋转80°,即使在狭窄的地方也能轻松移动。 强大的牵引力,实现舒适的操作性。
+水擦拭吸尘器用 主刷 替换刷头 旋转刷</t>
+        </is>
+      </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>B0GXZR4TNN</t>
+          <t>B0H6DZMNPV</t>
         </is>
       </c>
       <c r="M30" s="12" t="inlineStr">
@@ -14420,13 +14417,13 @@
         </is>
       </c>
       <c r="O30" s="13">
-        <v>2087</v>
+        <v>79262</v>
       </c>
       <c r="P30" s="13">
-        <v>102044</v>
+        <v>540152</v>
       </c>
       <c r="Q30" s="14">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="R30" s="15" t="inlineStr">
         <is>
@@ -14435,15 +14432,15 @@
       </c>
       <c r="S30" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T30" s="13">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U30" s="14"/>
       <c r="V30" s="13">
-        <v>80991</v>
+        <v>41862</v>
       </c>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
@@ -14451,37 +14448,29 @@
         <v>1</v>
       </c>
       <c r="Z30" s="13">
-        <v>8999</v>
+        <v>41862</v>
       </c>
       <c r="AA30" s="2"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="2"/>
-      <c r="AD30" s="17">
-        <v>30</v>
-      </c>
-      <c r="AE30" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="18">
-        <v>5</v>
-      </c>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="13"/>
+      <c r="AF30" s="18"/>
       <c r="AG30" s="19">
         <v>0</v>
       </c>
-      <c r="AH30" s="13">
-        <v>532</v>
-      </c>
+      <c r="AH30" s="13"/>
       <c r="AI30" s="14">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AL30" s="17">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="AM30" s="11" t="inlineStr">
         <is>
@@ -14492,14 +14481,14 @@
       <c r="AO30" s="11"/>
       <c r="AP30" s="2"/>
       <c r="AQ30" s="17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AR30" s="17">
         <v>1</v>
       </c>
       <c r="AS30" s="12" t="inlineStr">
         <is>
-          <t>HighWin LLC</t>
+          <t>Dreame公式ストア</t>
         </is>
       </c>
       <c r="AT30" s="11" t="inlineStr">
@@ -14514,12 +14503,12 @@
       </c>
       <c r="AV30" s="12" t="inlineStr">
         <is>
-          <t>HONG KONG HONG KONG 999077 HK</t>
+          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
         </is>
       </c>
       <c r="AW30" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
         </is>
       </c>
       <c r="AX30" s="11"/>
@@ -14527,66 +14516,22 @@
       <c r="AZ30" s="11"/>
       <c r="BA30" s="11"/>
       <c r="BB30" s="11"/>
-      <c r="BC30" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD30" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC30" s="11"/>
+      <c r="BD30" s="11"/>
       <c r="BE30" s="11"/>
-      <c r="BF30" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF30" s="11"/>
       <c r="BG30" s="11"/>
       <c r="BH30" s="12"/>
       <c r="BI30" s="20"/>
-      <c r="BJ30" s="20" t="inlineStr">
-        <is>
-          <t>4 千克</t>
-        </is>
-      </c>
+      <c r="BJ30" s="20"/>
       <c r="BK30" s="20"/>
-      <c r="BL30" s="20" t="inlineStr">
-        <is>
-          <t>19 x 41 x 30 cm</t>
-        </is>
-      </c>
-      <c r="BM30" s="20" t="inlineStr">
-        <is>
-          <t>19.00 x 41.00 x 30.00 cm</t>
-        </is>
-      </c>
-      <c r="BN30" s="20" t="inlineStr">
-        <is>
-          <t>4.1 kg</t>
-        </is>
-      </c>
-      <c r="BO30" s="20" t="inlineStr">
-        <is>
-          <t>4.10 kg</t>
-        </is>
-      </c>
-      <c r="BP30" s="20" t="inlineStr">
-        <is>
-          <t>41 x 30 x 19 cm</t>
-        </is>
-      </c>
-      <c r="BQ30" s="20" t="inlineStr">
-        <is>
-          <t>41.00 x 30.00 x 19.00 cm</t>
-        </is>
-      </c>
-      <c r="BR30" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BL30" s="20"/>
+      <c r="BM30" s="20"/>
+      <c r="BN30" s="20"/>
+      <c r="BO30" s="20"/>
+      <c r="BP30" s="20"/>
+      <c r="BQ30" s="20"/>
+      <c r="BR30" s="11"/>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
@@ -14595,45 +14540,50 @@
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>B0H6DZMNPV</t>
-        </is>
-      </c>
-      <c r="D31" s="12"/>
+          <t>B004D2ESD6</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>样式名称: 清洁剂 50ml (小)</t>
+        </is>
+      </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>ラッキーウッド(Luckywood)</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/ラッキーウッド-Luckywood/b/ref=bl_dp_s_web_24383112051?ie=UTF8&amp;node=24383112051&amp;field-lbr_brands_browse-bin=%E3%83%A9%E3%83%83%E3%82%AD%E3%83%BC%E3%82%A6%E3%83%83%E3%83%89%28Luckywood%29</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
+          <t>银清洁剂 50cc 0-29495-000</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>【2026年新上市! 】Dreame推出超薄多功能手持吸尘器。 适用于城市型住宅的紧凑设计,具备多种功能。 超薄多功能手持吸尘器T16,9.85厘米超薄机身和180°全平设计,能够轻松进入家具下方,发挥强大的吸力。 此外,轻量机身可以快速旋转80°,即使在狭窄的地方也能轻松移动。 强大的牵引力,实现舒适的操作性。
-水擦拭吸尘器用 主刷 替换刷头 旋转刷</t>
+          <t>6.5×Φ3.5
+0.07
+新潟县燕市</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B004D2ESD6?psc=1</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41rAwhmWDoL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>B0H6DZMNPV</t>
+          <t>B081F4CR4S</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
@@ -14647,13 +14597,13 @@
         </is>
       </c>
       <c r="O31" s="13">
-        <v>79262</v>
+        <v>62804</v>
       </c>
       <c r="P31" s="13">
-        <v>540152</v>
+        <v>4697</v>
       </c>
       <c r="Q31" s="14">
-        <v>0.89</v>
+        <v>0.29</v>
       </c>
       <c r="R31" s="15" t="inlineStr">
         <is>
@@ -14662,45 +14612,55 @@
       </c>
       <c r="S31" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T31" s="13">
-        <v>1</v>
-      </c>
-      <c r="U31" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="U31" s="14">
+        <v>0.59</v>
+      </c>
       <c r="V31" s="13">
-        <v>41862</v>
+        <v>32289</v>
       </c>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z31" s="13">
-        <v>41862</v>
+        <v>687</v>
       </c>
       <c r="AA31" s="2"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="2"/>
-      <c r="AD31" s="17"/>
-      <c r="AE31" s="13"/>
-      <c r="AF31" s="18"/>
+      <c r="AD31" s="17">
+        <v>45</v>
+      </c>
+      <c r="AE31" s="13">
+        <v>2</v>
+      </c>
+      <c r="AF31" s="18">
+        <v>4</v>
+      </c>
       <c r="AG31" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="13"/>
+        <v>0.0426</v>
+      </c>
+      <c r="AH31" s="13">
+        <v>252</v>
+      </c>
       <c r="AI31" s="14">
-        <v>0.85</v>
+        <v>0.48</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2015-12-07</t>
         </is>
       </c>
       <c r="AL31" s="17">
-        <v>97</v>
+        <v>3947</v>
       </c>
       <c r="AM31" s="11" t="inlineStr">
         <is>
@@ -14711,14 +14671,14 @@
       <c r="AO31" s="11"/>
       <c r="AP31" s="2"/>
       <c r="AQ31" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR31" s="17">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AS31" s="12" t="inlineStr">
         <is>
-          <t>Dreame公式ストア</t>
+          <t>一級品の店 いっきゅう</t>
         </is>
       </c>
       <c r="AT31" s="11" t="inlineStr">
@@ -14728,17 +14688,17 @@
       </c>
       <c r="AU31" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV31" s="12" t="inlineStr">
         <is>
-          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
+          <t>堺市 大阪府 5900934 JP</t>
         </is>
       </c>
       <c r="AW31" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SBGLLXVMPUPP</t>
         </is>
       </c>
       <c r="AX31" s="11"/>
@@ -14753,15 +14713,47 @@
       <c r="BG31" s="11"/>
       <c r="BH31" s="12"/>
       <c r="BI31" s="20"/>
-      <c r="BJ31" s="20"/>
+      <c r="BJ31" s="20" t="inlineStr">
+        <is>
+          <t>0.15 磅</t>
+        </is>
+      </c>
       <c r="BK31" s="20"/>
-      <c r="BL31" s="20"/>
-      <c r="BM31" s="20"/>
-      <c r="BN31" s="20"/>
-      <c r="BO31" s="20"/>
-      <c r="BP31" s="20"/>
-      <c r="BQ31" s="20"/>
-      <c r="BR31" s="11"/>
+      <c r="BL31" s="20" t="inlineStr">
+        <is>
+          <t>9.2 x 3.1 x 3.1 cm</t>
+        </is>
+      </c>
+      <c r="BM31" s="20" t="inlineStr">
+        <is>
+          <t>9.20 x 3.10 x 3.10 cm</t>
+        </is>
+      </c>
+      <c r="BN31" s="20" t="inlineStr">
+        <is>
+          <t>70 g</t>
+        </is>
+      </c>
+      <c r="BO31" s="20" t="inlineStr">
+        <is>
+          <t>70.00 g</t>
+        </is>
+      </c>
+      <c r="BP31" s="20" t="inlineStr">
+        <is>
+          <t>9.2 x 3.1 x 3.1 cm</t>
+        </is>
+      </c>
+      <c r="BQ31" s="20" t="inlineStr">
+        <is>
+          <t>9.20 x 3.10 x 3.10 cm</t>
+        </is>
+      </c>
+      <c r="BR31" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
@@ -14770,50 +14762,51 @@
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>B004D2ESD6</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>样式名称: 清洁剂 50ml (小)</t>
-        </is>
-      </c>
-      <c r="E32" s="12"/>
+          <t>B0183900C2</t>
+        </is>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>品牌: ＦＵＫＡＩ | 特殊功能: 无绳 | 筛选类型: 滤布 | 推荐表面: 家具装饰品 | 电源: 充电式</t>
+        </is>
+      </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>ラッキーウッド(Luckywood)</t>
+          <t>ＦＵＫＡＩ</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/ラッキーウッド-Luckywood/b/ref=bl_dp_s_web_24383112051?ie=UTF8&amp;node=24383112051&amp;field-lbr_brands_browse-bin=%E3%83%A9%E3%83%83%E3%82%AD%E3%83%BC%E3%82%A6%E3%83%83%E3%83%89%28Luckywood%29</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/FUKAI/page/834EE7E8-56E1-4105-8E98-045B52696442?lp_asin=B0183900C2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>银清洁剂 50cc 0-29495-000</t>
+          <t>FUKAI 充电式湿&amp;干式手持吸尘器 | 轻量 无线 强力吸力 简单充电 附带3种喷嘴 车内清洁 办公桌 FC-810</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>6.5×Φ3.5
-0.07
-新潟县燕市</t>
+          <t>干湿两用:可以吸出牛奶和果汁等液体。 最适合用于打湿、园艺等有水气的地方打扫。
+【轻量无线&amp;手持】轻量无线,轻松打扫。 小孩子和老年人也能轻松使用。
+无需纸袋,可水洗:集尘盒一键即可拆卸,方便丢弃垃圾。 也可以整体水洗。
+附带3种附件:附带缝隙吸头、吸嘴、3种带刷头的吸嘴。 侧边的缝隙和家具之间等细小场所也能轻松清洁。</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B004D2ESD6?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0183900C2?psc=1</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41rAwhmWDoL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31ZDf4xaXpL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>B081F4CR4S</t>
+          <t>B0183900C2</t>
         </is>
       </c>
       <c r="M32" s="12" t="inlineStr">
@@ -14827,13 +14820,11 @@
         </is>
       </c>
       <c r="O32" s="13">
-        <v>62804</v>
-      </c>
-      <c r="P32" s="13">
-        <v>4697</v>
-      </c>
+        <v>124616</v>
+      </c>
+      <c r="P32" s="13"/>
       <c r="Q32" s="14">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="R32" s="15" t="inlineStr">
         <is>
@@ -14842,56 +14833,38 @@
       </c>
       <c r="S32" s="16" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T32" s="13">
-        <v>47</v>
-      </c>
-      <c r="U32" s="14">
-        <v>0.59</v>
-      </c>
-      <c r="V32" s="13">
-        <v>32289</v>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T32" s="13"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="13"/>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="17">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="13">
-        <v>687</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z32" s="13"/>
       <c r="AA32" s="2"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="17">
-        <v>45</v>
-      </c>
-      <c r="AE32" s="13">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AE32" s="13"/>
       <c r="AF32" s="18">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AG32" s="19">
-        <v>0.0426</v>
-      </c>
-      <c r="AH32" s="13">
-        <v>252</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH32" s="13"/>
       <c r="AI32" s="14">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="AJ32"/>
-      <c r="AK32" s="11" t="inlineStr">
-        <is>
-          <t>2015-12-07</t>
-        </is>
-      </c>
-      <c r="AL32" s="17">
-        <v>3947</v>
-      </c>
+      <c r="AK32" s="11"/>
+      <c r="AL32" s="17"/>
       <c r="AM32" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -14900,37 +14873,17 @@
       <c r="AN32" s="11"/>
       <c r="AO32" s="11"/>
       <c r="AP32" s="2"/>
-      <c r="AQ32" s="17">
-        <v>6</v>
-      </c>
-      <c r="AR32" s="17">
-        <v>9</v>
-      </c>
-      <c r="AS32" s="12" t="inlineStr">
-        <is>
-          <t>一級品の店 いっきゅう</t>
-        </is>
-      </c>
+      <c r="AQ32" s="17"/>
+      <c r="AR32" s="17"/>
+      <c r="AS32" s="12"/>
       <c r="AT32" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU32" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV32" s="12" t="inlineStr">
-        <is>
-          <t>堺市 大阪府 5900934 JP</t>
-        </is>
-      </c>
-      <c r="AW32" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SBGLLXVMPUPP</t>
-        </is>
-      </c>
+      <c r="AU32" s="11"/>
+      <c r="AV32" s="12"/>
+      <c r="AW32" s="11"/>
       <c r="AX32" s="11"/>
       <c r="AY32" s="11"/>
       <c r="AZ32" s="11"/>
@@ -14945,45 +14898,17 @@
       <c r="BI32" s="20"/>
       <c r="BJ32" s="20" t="inlineStr">
         <is>
-          <t>0.15 磅</t>
+          <t>0.8 千克</t>
         </is>
       </c>
       <c r="BK32" s="20"/>
-      <c r="BL32" s="20" t="inlineStr">
-        <is>
-          <t>9.2 x 3.1 x 3.1 cm</t>
-        </is>
-      </c>
-      <c r="BM32" s="20" t="inlineStr">
-        <is>
-          <t>9.20 x 3.10 x 3.10 cm</t>
-        </is>
-      </c>
-      <c r="BN32" s="20" t="inlineStr">
-        <is>
-          <t>70 g</t>
-        </is>
-      </c>
-      <c r="BO32" s="20" t="inlineStr">
-        <is>
-          <t>70.00 g</t>
-        </is>
-      </c>
-      <c r="BP32" s="20" t="inlineStr">
-        <is>
-          <t>9.2 x 3.1 x 3.1 cm</t>
-        </is>
-      </c>
-      <c r="BQ32" s="20" t="inlineStr">
-        <is>
-          <t>9.20 x 3.10 x 3.10 cm</t>
-        </is>
-      </c>
-      <c r="BR32" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BL32" s="20"/>
+      <c r="BM32" s="20"/>
+      <c r="BN32" s="20"/>
+      <c r="BO32" s="20"/>
+      <c r="BP32" s="20"/>
+      <c r="BQ32" s="20"/>
+      <c r="BR32" s="11"/>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
@@ -14992,51 +14917,56 @@
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>B0183900C2</t>
-        </is>
-      </c>
-      <c r="D33" s="12"/>
+          <t>B08MDZSSDP</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>颜色: 蓝色</t>
+        </is>
+      </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>品牌: ＦＵＫＡＩ | 特殊功能: 无绳 | 筛选类型: 滤布 | 推荐表面: 家具装饰品 | 电源: 充电式</t>
+          <t>品牌: DEKOprojp | 特殊功能: HEPA, 便携式, 干湿两用, 紧凑型, 轻巧 | 推荐表面: 家具装饰品 | 电源: 电池供电 | 随附部件: 日语使用说明书* 1 延长软管* 1 平管* 1 刷头旋钮* 1 USB充电线* 1 便携袋* 1</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>ＦＵＫＡＩ</t>
+          <t>DEKOprojp</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/FUKAI/page/834EE7E8-56E1-4105-8E98-045B52696442?lp_asin=B0183900C2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=DEKOprojp</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>FUKAI 充电式湿&amp;干式手持吸尘器 | 轻量 无线 强力吸力 简单充电 附带3种喷嘴 车内清洁 办公桌 FC-810</t>
+          <t>DEKOPRO 手持吸尘器 无绳吸尘器 迷你吸尘器 干湿两用 5200pa 轻巧 小巧 可续航25分钟 充电式 车用 家用 室内装饰 时尚 无线 独居 HEPA过滤器 附收纳袋 蓝色</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>干湿两用:可以吸出牛奶和果汁等液体。 最适合用于打湿、园艺等有水气的地方打扫。
-【轻量无线&amp;手持】轻量无线,轻松打扫。 小孩子和老年人也能轻松使用。
-无需纸袋,可水洗:集尘盒一键即可拆卸,方便丢弃垃圾。 也可以整体水洗。
-附带3种附件:附带缝隙吸头、吸嘴、3种带刷头的吸嘴。 侧边的缝隙和家具之间等细小场所也能轻松清洁。</t>
+          <t>【吸力超群&amp;排气清洁】搭载120w高性能马达,吸尘功率很高! 最大5500PA的超强吸力,不仅可以吸收座椅的灰尘和垃圾,还可以清除进入垫子里的沙子和土等。 集尘方式为过滤式,清扫过程中排气比较干净。 附带的优异的HEPA过滤器可以反复使用。 即使集尘杯满了,吸力不易掉落,可以直接丢弃垃圾。 吸引力满足各种人士。
+【小巧&amp;超轻】比1千克更轻,即使是女性和儿童也能轻松清扫。 老年人也不用担心手臂或肩膀疼痛。 收纳也很小巧。 小巧,放在车内的某处,即使担心小垃圾也能单手拿着,所以不用担心会觉得"大肚子"。
+保养简单:采用HEPA滤网,可反复水洗使用。 而且还带有备用过滤网,所以更放心。 通过过滤器捕捉吸引的灰尘、花粉等垃圾,排出干净空气。 只需丢弃集尘杯的垃圾,就可以在过滤网上留下灰尘。 用附带的清洁刷擦拭过滤器,就可以去除灰尘并预防吸引力下降。 可用水清洗灰尘杯和滤网。 易于清洁!
+【3种喷嘴可广泛使用】 70厘米长缝隙喷嘴、液体&amp;缝隙用喷嘴、3种刷头配件。 在窗子的缝隙、角落、家具和墙壁之间、车内等一般狭窄的地方都能轻松清洁干净。 替换附带的喷嘴,各个角落都能保持干净。 没有麻烦的电线,想清扫的地方都可以接到任何地方。
+【包装内容】 日语使用说明书* 1 延长管* 1 平管* 1 刷鼓管* 1 吸尘器主体* 1 USB充电线* 1 便携袋* 1 万一出现不良或质量问题,请与我们联系。</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0183900C2?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08MDZSSDP?psc=1</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31ZDf4xaXpL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31rTP7TuVHL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>B0183900C2</t>
+          <t>B08RYKLST5</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
@@ -15050,7 +14980,7 @@
         </is>
       </c>
       <c r="O33" s="13">
-        <v>124616</v>
+        <v>112034</v>
       </c>
       <c r="P33" s="13"/>
       <c r="Q33" s="14">
@@ -15063,7 +14993,7 @@
       </c>
       <c r="S33" s="16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T33" s="13"/>
@@ -15079,11 +15009,11 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="17">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="AE33" s="13"/>
       <c r="AF33" s="18">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AG33" s="19">
         <v>0</v>
@@ -15119,18 +15049,18 @@
       <c r="AZ33" s="11"/>
       <c r="BA33" s="11"/>
       <c r="BB33" s="11"/>
-      <c r="BC33" s="11"/>
+      <c r="BC33" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD33" s="11"/>
       <c r="BE33" s="11"/>
       <c r="BF33" s="11"/>
       <c r="BG33" s="11"/>
       <c r="BH33" s="12"/>
       <c r="BI33" s="20"/>
-      <c r="BJ33" s="20" t="inlineStr">
-        <is>
-          <t>0.8 千克</t>
-        </is>
-      </c>
+      <c r="BJ33" s="20"/>
       <c r="BK33" s="20"/>
       <c r="BL33" s="20"/>
       <c r="BM33" s="20"/>
@@ -15147,56 +15077,52 @@
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>B08MDZSSDP</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>颜色: 蓝色</t>
-        </is>
-      </c>
+          <t>B0C4HGZ1L6</t>
+        </is>
+      </c>
+      <c r="D34" s="12"/>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>品牌: DEKOprojp | 特殊功能: HEPA, 便携式, 干湿两用, 紧凑型, 轻巧 | 推荐表面: 家具装饰品 | 电源: 电池供电 | 随附部件: 日语使用说明书* 1 延长软管* 1 平管* 1 刷头旋钮* 1 USB充电线* 1 便携袋* 1</t>
+          <t>品牌: NEODIT | 颜色: 白色 | 商品尺寸: 18深度 x 35宽度 x 29高度 厘米 | 型号名称: PCC01 | 电源: 有线电动</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>DEKOprojp</t>
+          <t>NEODIT</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=DEKOprojp</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>DEKOPRO 手持吸尘器 无绳吸尘器 迷你吸尘器 干湿两用 5200pa 轻巧 小巧 可续航25分钟 充电式 车用 家用 室内装饰 时尚 无线 独居 HEPA过滤器 附收纳袋 蓝色</t>
+          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>【吸力超群&amp;排气清洁】搭载120w高性能马达,吸尘功率很高! 最大5500PA的超强吸力,不仅可以吸收座椅的灰尘和垃圾,还可以清除进入垫子里的沙子和土等。 集尘方式为过滤式,清扫过程中排气比较干净。 附带的优异的HEPA过滤器可以反复使用。 即使集尘杯满了,吸力不易掉落,可以直接丢弃垃圾。 吸引力满足各种人士。
-【小巧&amp;超轻】比1千克更轻,即使是女性和儿童也能轻松清扫。 老年人也不用担心手臂或肩膀疼痛。 收纳也很小巧。 小巧,放在车内的某处,即使担心小垃圾也能单手拿着,所以不用担心会觉得"大肚子"。
-保养简单:采用HEPA滤网,可反复水洗使用。 而且还带有备用过滤网,所以更放心。 通过过滤器捕捉吸引的灰尘、花粉等垃圾,排出干净空气。 只需丢弃集尘杯的垃圾,就可以在过滤网上留下灰尘。 用附带的清洁刷擦拭过滤器,就可以去除灰尘并预防吸引力下降。 可用水清洗灰尘杯和滤网。 易于清洁!
-【3种喷嘴可广泛使用】 70厘米长缝隙喷嘴、液体&amp;缝隙用喷嘴、3种刷头配件。 在窗子的缝隙、角落、家具和墙壁之间、车内等一般狭窄的地方都能轻松清洁干净。 替换附带的喷嘴,各个角落都能保持干净。 没有麻烦的电线,想清扫的地方都可以接到任何地方。
-【包装内容】 日语使用说明书* 1 延长管* 1 平管* 1 刷鼓管* 1 吸尘器主体* 1 USB充电线* 1 便携袋* 1 万一出现不良或质量问题,请与我们联系。</t>
+          <t>超强水平14KPa强力吸力:14000Pa强劲吸力,能够一气吸收污垢。 吸收液体时,由于需要吸收力,所以14000Pa的吸力很干爽,黏着不湿,干燥时可缩短时间。 让污垢浮起,水一起吸干,即使不洗的东西也变得很干净
+【不易漏水的构造】考虑到在清洁过程中避免弄脏水被溢出而开发本产品。 本产品软管与主体连接部分、水箱和主体的连接部分不易漏水。 接合部牢固固定,不易漏水,消除漏水烦恼,漏水时佩戴舒适,带有防漏的密封圈)
+【带两个刷头】由于是一体刷头,一体式刷头,可以一边清洁污垢。 用刷子擦干后吸一下就会大吃地去除污垢。 附带两个刷头,可以根据使用场景选择刷头。 大面积弄脏时,只需使用T头即可轻松清洗。 不脏手也可以轻松去除污垢。
+附带大容量的水箱:1080毫升,储蓄罐为850毫升。 因为不频繁更换水,所以长时间使用困难,大幅缩短作业时间。 看到吸取的污垢,看起来像污水储在罐里,非常舒适。 (注意:请不要使用回收罐装满水线。 脏水过多可能会导致漏水。)
+【包装内容】主体*1、刷头*2、防漏环*2。 线长:3米,软管长度:1.2米。 可以卷起来,不会破坏收纳的设计。 主体尺寸:35*29*18厘米,方便存放在狭窄的地方。 即使是地毯、沙发、汽车座椅的汗水桶等家庭用洗衣机放入的尺寸物品,也推荐给那些想在狭窄的房子里很重要的人。 如有任何问题或质量问题,请随时与我们联系。</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B08MDZSSDP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31rTP7TuVHL._AC_US200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>B08RYKLST5</t>
+          <t>B0CQCGX9DX</t>
         </is>
       </c>
       <c r="M34" s="12" t="inlineStr">
@@ -15210,11 +15136,13 @@
         </is>
       </c>
       <c r="O34" s="13">
-        <v>112034</v>
-      </c>
-      <c r="P34" s="13"/>
+        <v>177166</v>
+      </c>
+      <c r="P34" s="13">
+        <v>-1650</v>
+      </c>
       <c r="Q34" s="14">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R34" s="15" t="inlineStr">
         <is>
@@ -15223,7 +15151,7 @@
       </c>
       <c r="S34" s="16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T34" s="13"/>
@@ -15234,27 +15162,39 @@
       <c r="Y34" s="17">
         <v>1</v>
       </c>
-      <c r="Z34" s="13"/>
+      <c r="Z34" s="13">
+        <v>13998</v>
+      </c>
       <c r="AA34" s="2"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="17">
-        <v>77</v>
-      </c>
-      <c r="AE34" s="13"/>
+        <v>321</v>
+      </c>
+      <c r="AE34" s="13">
+        <v>0</v>
+      </c>
       <c r="AF34" s="18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG34" s="19">
         <v>0</v>
       </c>
-      <c r="AH34" s="13"/>
+      <c r="AH34" s="13">
+        <v>781</v>
+      </c>
       <c r="AI34" s="14">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AJ34"/>
-      <c r="AK34" s="11"/>
-      <c r="AL34" s="17"/>
+      <c r="AK34" s="11" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AL34" s="17">
+        <v>1187</v>
+      </c>
       <c r="AM34" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -15263,17 +15203,37 @@
       <c r="AN34" s="11"/>
       <c r="AO34" s="11"/>
       <c r="AP34" s="2"/>
-      <c r="AQ34" s="17"/>
-      <c r="AR34" s="17"/>
-      <c r="AS34" s="12"/>
+      <c r="AQ34" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR34" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS34" s="12" t="inlineStr">
+        <is>
+          <t>Neodit-tools</t>
+        </is>
+      </c>
       <c r="AT34" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU34" s="11"/>
-      <c r="AV34" s="12"/>
-      <c r="AW34" s="11"/>
+      <c r="AU34" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV34" s="12" t="inlineStr">
+        <is>
+          <t>nanjingshi jiangsusheng 210043 CN</t>
+        </is>
+      </c>
+      <c r="AW34" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U</t>
+        </is>
+      </c>
       <c r="AX34" s="11"/>
       <c r="AY34" s="11"/>
       <c r="AZ34" s="11"/>
@@ -15284,21 +15244,65 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD34" s="11"/>
+      <c r="BD34" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE34" s="11"/>
-      <c r="BF34" s="11"/>
+      <c r="BF34" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG34" s="11"/>
       <c r="BH34" s="12"/>
       <c r="BI34" s="20"/>
-      <c r="BJ34" s="20"/>
-      <c r="BK34" s="20"/>
-      <c r="BL34" s="20"/>
-      <c r="BM34" s="20"/>
-      <c r="BN34" s="20"/>
-      <c r="BO34" s="20"/>
-      <c r="BP34" s="20"/>
-      <c r="BQ34" s="20"/>
-      <c r="BR34" s="11"/>
+      <c r="BJ34" s="20" t="inlineStr">
+        <is>
+          <t>5.24 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK34" s="20" t="inlineStr">
+        <is>
+          <t>5.24 kg</t>
+        </is>
+      </c>
+      <c r="BL34" s="20" t="inlineStr">
+        <is>
+          <t>18 x 35 x 29 cm</t>
+        </is>
+      </c>
+      <c r="BM34" s="20" t="inlineStr">
+        <is>
+          <t>18.00 x 35.00 x 29.00 cm</t>
+        </is>
+      </c>
+      <c r="BN34" s="20" t="inlineStr">
+        <is>
+          <t>5.24 kg</t>
+        </is>
+      </c>
+      <c r="BO34" s="20" t="inlineStr">
+        <is>
+          <t>5.24 kg</t>
+        </is>
+      </c>
+      <c r="BP34" s="20" t="inlineStr">
+        <is>
+          <t>37.9 x 36.9 x 26.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ34" s="20" t="inlineStr">
+        <is>
+          <t>37.90 x 36.90 x 26.20 cm</t>
+        </is>
+      </c>
+      <c r="BR34" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
@@ -15307,52 +15311,52 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0C4HGZ1L6</t>
+          <t>B0CF9P7W51</t>
         </is>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>品牌: NEODIT | 颜色: 白色 | 商品尺寸: 18深度 x 35宽度 x 29高度 厘米 | 型号名称: PCC01 | 电源: 有线电动</t>
+          <t>品牌: Tineco | 特殊功能: 干湿两用 | 筛选类型: HEPA滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>NEODIT</t>
+          <t>Tineco</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B0CF9P7W51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
+          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>超强水平14KPa强力吸力:14000Pa强劲吸力,能够一气吸收污垢。 吸收液体时,由于需要吸收力,所以14000Pa的吸力很干爽,黏着不湿,干燥时可缩短时间。 让污垢浮起,水一起吸干,即使不洗的东西也变得很干净
-【不易漏水的构造】考虑到在清洁过程中避免弄脏水被溢出而开发本产品。 本产品软管与主体连接部分、水箱和主体的连接部分不易漏水。 接合部牢固固定,不易漏水,消除漏水烦恼,漏水时佩戴舒适,带有防漏的密封圈)
-【带两个刷头】由于是一体刷头,一体式刷头,可以一边清洁污垢。 用刷子擦干后吸一下就会大吃地去除污垢。 附带两个刷头,可以根据使用场景选择刷头。 大面积弄脏时,只需使用T头即可轻松清洗。 不脏手也可以轻松去除污垢。
-附带大容量的水箱:1080毫升,储蓄罐为850毫升。 因为不频繁更换水,所以长时间使用困难,大幅缩短作业时间。 看到吸取的污垢,看起来像污水储在罐里,非常舒适。 (注意:请不要使用回收罐装满水线。 脏水过多可能会导致漏水。)
-【包装内容】主体*1、刷头*2、防漏环*2。 线长:3米,软管长度:1.2米。 可以卷起来,不会破坏收纳的设计。 主体尺寸:35*29*18厘米,方便存放在狭窄的地方。 即使是地毯、沙发、汽车座椅的汗水桶等家庭用洗衣机放入的尺寸物品,也推荐给那些想在狭窄的房子里很重要的人。 如有任何问题或质量问题,请随时与我们联系。</t>
+          <t>【用于擦拭+吸力一台】日常生活中出入、家具移动、孩子游戏等各种污渍、地板的粘附污垢。 只需1台即可应对各种地板材料,简单高效的打扫,提高效率。
+【创新TINECO MHCBS技术】通过美丽的水和1分钟450旋转的高速拖把,手擦拭更彻底干净。 轻松享受新的家务体验。 新改良的浮动刮刀能够均匀去除滚筒刷的污垢,防止垃圾附着。
+一键自动清洁:自动清洁,能够彻底清洁滚筒刷和软管,实现彻底的维护。 清洗后,利用离心力干燥,有效去除滚筒中的水分,保持干燥状态,保持卫生和异味的生活。
+【创新的滚轮刷头设计】通过升级的双面滚轮刷,能够在墙壁上清扫干净,墙壁时也不会漏尘。
+【Tineco iLoop智能传感器技术】创新Tineco iLoop智能传感器,可根据污渍情况自动调节水量和功率。 TINECO iLoop智能传感器不够清洁吸尘器和拖把,清扫效率会降低,清扫的麻烦。</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/318f4iR6OhL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0CQCGX9DX</t>
+          <t>B0CF9P7W51</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
@@ -15366,13 +15370,11 @@
         </is>
       </c>
       <c r="O35" s="13">
-        <v>177166</v>
-      </c>
-      <c r="P35" s="13">
-        <v>-1650</v>
-      </c>
+        <v>181137</v>
+      </c>
+      <c r="P35" s="13"/>
       <c r="Q35" s="14">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
@@ -15381,7 +15383,7 @@
       </c>
       <c r="S35" s="16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T35" s="13"/>
@@ -15392,39 +15394,27 @@
       <c r="Y35" s="17">
         <v>1</v>
       </c>
-      <c r="Z35" s="13">
-        <v>13998</v>
-      </c>
+      <c r="Z35" s="13"/>
       <c r="AA35" s="2"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="17">
-        <v>321</v>
-      </c>
-      <c r="AE35" s="13">
-        <v>0</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="AE35" s="13"/>
       <c r="AF35" s="18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG35" s="19">
         <v>0</v>
       </c>
-      <c r="AH35" s="13">
-        <v>781</v>
-      </c>
+      <c r="AH35" s="13"/>
       <c r="AI35" s="14">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AJ35"/>
-      <c r="AK35" s="11" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="AL35" s="17">
-        <v>1187</v>
-      </c>
+      <c r="AK35" s="11"/>
+      <c r="AL35" s="17"/>
       <c r="AM35" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -15433,37 +15423,17 @@
       <c r="AN35" s="11"/>
       <c r="AO35" s="11"/>
       <c r="AP35" s="2"/>
-      <c r="AQ35" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR35" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS35" s="12" t="inlineStr">
-        <is>
-          <t>Neodit-tools</t>
-        </is>
-      </c>
+      <c r="AQ35" s="17"/>
+      <c r="AR35" s="17"/>
+      <c r="AS35" s="12"/>
       <c r="AT35" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU35" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV35" s="12" t="inlineStr">
-        <is>
-          <t>nanjingshi jiangsusheng 210043 CN</t>
-        </is>
-      </c>
-      <c r="AW35" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U</t>
-        </is>
-      </c>
+      <c r="AU35" s="11"/>
+      <c r="AV35" s="12"/>
+      <c r="AW35" s="11"/>
       <c r="AX35" s="11"/>
       <c r="AY35" s="11"/>
       <c r="AZ35" s="11"/>
@@ -15474,65 +15444,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD35" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD35" s="11"/>
       <c r="BE35" s="11"/>
-      <c r="BF35" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF35" s="11"/>
       <c r="BG35" s="11"/>
       <c r="BH35" s="12"/>
       <c r="BI35" s="20"/>
-      <c r="BJ35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BL35" s="20" t="inlineStr">
-        <is>
-          <t>18 x 35 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="20" t="inlineStr">
-        <is>
-          <t>18.00 x 35.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BN35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BO35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BP35" s="20" t="inlineStr">
-        <is>
-          <t>37.9 x 36.9 x 26.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ35" s="20" t="inlineStr">
-        <is>
-          <t>37.90 x 36.90 x 26.20 cm</t>
-        </is>
-      </c>
-      <c r="BR35" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BJ35" s="20"/>
+      <c r="BK35" s="20"/>
+      <c r="BL35" s="20"/>
+      <c r="BM35" s="20"/>
+      <c r="BN35" s="20"/>
+      <c r="BO35" s="20"/>
+      <c r="BP35" s="20"/>
+      <c r="BQ35" s="20"/>
+      <c r="BR35" s="11"/>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
@@ -15541,52 +15467,52 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0D5HBSJFX</t>
         </is>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>品牌: Tineco | 特殊功能: 干湿两用 | 筛选类型: HEPA滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
+          <t>品牌: dreame | 特殊功能: 干湿两用 | 筛选类型: HEPA滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>Tineco</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B0CF9P7W51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
+          <t>dreame (ドリーミー) H12S 湿拖吸尘器 吸尘&amp;湿拖2in1 刷头自动清洗和温风干燥 除菌 贴墙边刷头设计 16000Pa强力吸力 35分钟连续运行 智能污垢检测和自动吸力调整 大容量水箱 语音导航 高速电机 静音设计 3种运行模式 专用清洁剂</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>【用于擦拭+吸力一台】日常生活中出入、家具移动、孩子游戏等各种污渍、地板的粘附污垢。 只需1台即可应对各种地板材料,简单高效的打扫,提高效率。
-【创新TINECO MHCBS技术】通过美丽的水和1分钟450旋转的高速拖把,手擦拭更彻底干净。 轻松享受新的家务体验。 新改良的浮动刮刀能够均匀去除滚筒刷的污垢,防止垃圾附着。
-一键自动清洁:自动清洁,能够彻底清洁滚筒刷和软管,实现彻底的维护。 清洗后,利用离心力干燥,有效去除滚筒中的水分,保持干燥状态,保持卫生和异味的生活。
-【创新的滚轮刷头设计】通过升级的双面滚轮刷,能够在墙壁上清扫干净,墙壁时也不会漏尘。
-【Tineco iLoop智能传感器技术】创新Tineco iLoop智能传感器,可根据污渍情况自动调节水量和功率。 TINECO iLoop智能传感器不够清洁吸尘器和拖把,清扫效率会降低,清扫的麻烦。</t>
+          <t>【美丽地覆盖每一个角落】H12S 采用改良的刷头设计，能够牢牢接触到距离墙6毫米的边缘。 迄今为止难以到达的房间的角落里常年留下的污垢,精心彻底的干净整洁。
+【自动清洁和消毒，保持刷子始终清洁】自动刷子清洁功能全自动完成刷子的清洗、冲洗和干燥，无需手动清洗刷子。 智能的水循环系统生成电解水,亦可用于旋转刷的自我清洗。 除菌率最大99.99%。 此外,还搭载了新Dreame独特的银离子抗菌刷头(抗菌率&gt;99.99%),与55°C的温风干燥组合,彻底防止旋转刷上的细菌增殖,进一步加强了抗菌、防臭功能。
+【实现高效的打扫,强力吸力】即使是湿的污垢,干的污垢,16 kPa 的强劲吸力,同时擦拭的k清洁性能,让咖啡豆和谷物变得清爽干净。 拖地后几乎不留下水痕，对地板的负担也很轻。
+【根据污垢自动调整吸力】H12S智能传感器可以检测湿润污垢和干燥污垢。 根据污垢的种类和量自动优化吸引力,抑制功率消耗,同时兼顾清洁效率和成品的美感。
+【三种模式可应对干净污垢和湿污垢】基本清洁使用“自动清洁模式”，想要去除肉眼看不见的污垢时使用“除菌模式”，只想吸取液体时使用“吸引模式”的三种模式可供选择。 无论是干燥粘附的污垢还是溢出的食物污渍，都可以轻松清洁。</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/318f4iR6OhL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31gWtVLKoDL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0D5HBSJFX</t>
         </is>
       </c>
       <c r="M36" s="12" t="inlineStr">
@@ -15600,7 +15526,7 @@
         </is>
       </c>
       <c r="O36" s="13">
-        <v>181137</v>
+        <v>99191</v>
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="14">
@@ -15613,7 +15539,7 @@
       </c>
       <c r="S36" s="16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T36" s="13"/>
@@ -15629,11 +15555,11 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="17">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="AE36" s="13"/>
       <c r="AF36" s="18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG36" s="19">
         <v>0</v>
@@ -15674,9 +15600,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD36" s="11"/>
+      <c r="BD36" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE36" s="11"/>
-      <c r="BF36" s="11"/>
+      <c r="BF36" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG36" s="11"/>
       <c r="BH36" s="12"/>
       <c r="BI36" s="20"/>
@@ -15697,52 +15631,51 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B0D5HBSJFX</t>
+          <t>B0FGC7422M</t>
         </is>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>品牌: dreame | 特殊功能: 干湿两用 | 筛选类型: HEPA滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
+          <t>品牌: JONR | 特殊功能: 低噪音, 可充电, 干湿两用, 无绳, 自動推進 | 筛选类型: HEPA滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>dreame (ドリーミー) H12S 湿拖吸尘器 吸尘&amp;湿拖2in1 刷头自动清洗和温风干燥 除菌 贴墙边刷头设计 16000Pa强力吸力 35分钟连续运行 智能污垢检测和自动吸力调整 大容量水箱 语音导航 高速电机 静音设计 3种运行模式 专用清洁剂</t>
+          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>【美丽地覆盖每一个角落】H12S 采用改良的刷头设计，能够牢牢接触到距离墙6毫米的边缘。 迄今为止难以到达的房间的角落里常年留下的污垢,精心彻底的干净整洁。
-【自动清洁和消毒，保持刷子始终清洁】自动刷子清洁功能全自动完成刷子的清洗、冲洗和干燥，无需手动清洗刷子。 智能的水循环系统生成电解水,亦可用于旋转刷的自我清洗。 除菌率最大99.99%。 此外,还搭载了新Dreame独特的银离子抗菌刷头(抗菌率&gt;99.99%),与55°C的温风干燥组合,彻底防止旋转刷上的细菌增殖,进一步加强了抗菌、防臭功能。
-【实现高效的打扫,强力吸力】即使是湿的污垢,干的污垢,16 kPa 的强劲吸力,同时擦拭的k清洁性能,让咖啡豆和谷物变得清爽干净。 拖地后几乎不留下水痕，对地板的负担也很轻。
-【根据污垢自动调整吸力】H12S智能传感器可以检测湿润污垢和干燥污垢。 根据污垢的种类和量自动优化吸引力,抑制功率消耗,同时兼顾清洁效率和成品的美感。
-【三种模式可应对干净污垢和湿污垢】基本清洁使用“自动清洁模式”，想要去除肉眼看不见的污垢时使用“除菌模式”，只想吸取液体时使用“吸引模式”的三种模式可供选择。 无论是干燥粘附的污垢还是溢出的食物污渍，都可以轻松清洁。</t>
+          <t>【高效化每天的清扫*不错过这个垃圾! 日本最轻的擦拭吸尘器"JONR ED12 Lite"搭载了特殊设计的滚轮和"边缘对应刷子"。 只有1mm的空隙和墙壁时,地板的角落等很难保养的狭窄的地方也能很好地进行探索。 以往,不仅可以去除灰尘和顽固污渍,还能够充分吸收液体状污垢和粘腻的污垢,同时用水擦拭。 只需一次擦拭即可完成,无需花费功夫,节省维护时间。 将床打磨成闪亮状态。 适用于时短和家务效率的理想家电。 一个人生活的最佳选择。
+【吸力+擦拭*2in1一体式吸尘器】"JONR ED12 Lite"是一款可同时吸&amp;擦拭水分的2in1无线直立式吸尘器设计的创意产品。 基于人体工程学的手柄和下重心设计,无需复杂操作的直观操作。 老年人也可放心使用! 长时间使用手腕也不易疲劳的设计。 滚轮刷延伸至前方,自走式,墙壁和桌腿周围,家具的缝隙也能彻底清洁干净。 17,000 Pa的强力吸力,可同时使用吸尘器和拖把,大幅缩短清洁地板时间。 搭载2600mAh的大容量电池和850毫升的清水罐+450毫升的污水箱,可连续工作45分钟,无需频繁加水。 清洁完毕后请自动清洗滚轮刷。 无需繁琐的打扫后,您可以在忙碌的日常保持家清洁。
+【强大的功能,更放心的清洁】抗菌规格的滚轮刷能够抑制细菌的产生! 电解水生成装置的水箱,就可以期待除菌效果! ,紧贴地板的浮动刮刀能够彻底清除细小的垃圾,实现零擦拭残留。 家人的健康保护家居防护。
+[适用于多种地板 * 各种污垢和垃圾] 不仅可以擦拭水,还可以去除地板面的垃圾和污渍。 适用地板材料:聚氯乙烯地板(聚氯乙烯地板)、榻榻米、瓷砖、大理石、地板等。 适用污渍/垃圾:毛发、液体污垢、土壤、沙子、食物溢出、液体污渍、宠物粗相等。 不用担心宝宝会被食物洒落或宠物毛散落的点心!</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31gWtVLKoDL._AC_US200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>B0D5HBSJFX</t>
+          <t>B0FGC7422M</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
@@ -15756,11 +15689,13 @@
         </is>
       </c>
       <c r="O37" s="13">
-        <v>99191</v>
-      </c>
-      <c r="P37" s="13"/>
+        <v>160439</v>
+      </c>
+      <c r="P37" s="13">
+        <v>4124</v>
+      </c>
       <c r="Q37" s="14">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R37" s="15" t="inlineStr">
         <is>
@@ -15769,7 +15704,7 @@
       </c>
       <c r="S37" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T37" s="13"/>
@@ -15780,27 +15715,39 @@
       <c r="Y37" s="17">
         <v>1</v>
       </c>
-      <c r="Z37" s="13"/>
+      <c r="Z37" s="13">
+        <v>118000</v>
+      </c>
       <c r="AA37" s="2"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="17">
-        <v>80</v>
-      </c>
-      <c r="AE37" s="13"/>
+        <v>29</v>
+      </c>
+      <c r="AE37" s="13">
+        <v>2</v>
+      </c>
       <c r="AF37" s="18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AG37" s="19">
         <v>0</v>
       </c>
-      <c r="AH37" s="13"/>
+      <c r="AH37" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI37" s="14">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AJ37"/>
-      <c r="AK37" s="11"/>
-      <c r="AL37" s="17"/>
+      <c r="AK37" s="11" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AL37" s="17">
+        <v>434</v>
+      </c>
       <c r="AM37" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -15809,27 +15756,43 @@
       <c r="AN37" s="11"/>
       <c r="AO37" s="11"/>
       <c r="AP37" s="2"/>
-      <c r="AQ37" s="17"/>
-      <c r="AR37" s="17"/>
-      <c r="AS37" s="12"/>
+      <c r="AQ37" s="17">
+        <v>8</v>
+      </c>
+      <c r="AR37" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS37" s="12" t="inlineStr">
+        <is>
+          <t>-公式ストア</t>
+        </is>
+      </c>
       <c r="AT37" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU37" s="11"/>
-      <c r="AV37" s="12"/>
-      <c r="AW37" s="11"/>
+      <c r="AU37" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV37" s="12" t="inlineStr">
+        <is>
+          <t>莆田市 福建 351119 CN</t>
+        </is>
+      </c>
+      <c r="AW37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6</t>
+        </is>
+      </c>
       <c r="AX37" s="11"/>
       <c r="AY37" s="11"/>
       <c r="AZ37" s="11"/>
       <c r="BA37" s="11"/>
       <c r="BB37" s="11"/>
-      <c r="BC37" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC37" s="11"/>
       <c r="BD37" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15844,15 +15807,47 @@
       <c r="BG37" s="11"/>
       <c r="BH37" s="12"/>
       <c r="BI37" s="20"/>
-      <c r="BJ37" s="20"/>
-      <c r="BK37" s="20"/>
-      <c r="BL37" s="20"/>
+      <c r="BJ37" s="20" t="inlineStr">
+        <is>
+          <t>3 kg</t>
+        </is>
+      </c>
+      <c r="BK37" s="20" t="inlineStr">
+        <is>
+          <t>3.00 kg</t>
+        </is>
+      </c>
+      <c r="BL37" s="20" t="inlineStr">
+        <is>
+          <t>29.6長さ x 26.9幅 x 113.4高さ cm</t>
+        </is>
+      </c>
       <c r="BM37" s="20"/>
-      <c r="BN37" s="20"/>
-      <c r="BO37" s="20"/>
-      <c r="BP37" s="20"/>
-      <c r="BQ37" s="20"/>
-      <c r="BR37" s="11"/>
+      <c r="BN37" s="20" t="inlineStr">
+        <is>
+          <t>5.96 kg</t>
+        </is>
+      </c>
+      <c r="BO37" s="20" t="inlineStr">
+        <is>
+          <t>5.96 kg</t>
+        </is>
+      </c>
+      <c r="BP37" s="20" t="inlineStr">
+        <is>
+          <t>55.4 x 33.7 x 31.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ37" s="20" t="inlineStr">
+        <is>
+          <t>55.40 x 33.70 x 31.20 cm</t>
+        </is>
+      </c>
+      <c r="BR37" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
@@ -15861,13 +15856,13 @@
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
+          <t>B0FL2KXDMX</t>
         </is>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>品牌: JONR | 特殊功能: 低噪音, 可充电, 干湿两用, 无绳, 自動推進 | 筛选类型: HEPA滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
+          <t>品牌: JONR | 特殊功能: 干湿两用, 无线, 自行驶式, 轻巧, 轻量级 | 筛选类型: 滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -15877,35 +15872,32 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
+          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>【高效化每天的清扫*不错过这个垃圾! 日本最轻的擦拭吸尘器"JONR ED12 Lite"搭载了特殊设计的滚轮和"边缘对应刷子"。 只有1mm的空隙和墙壁时,地板的角落等很难保养的狭窄的地方也能很好地进行探索。 以往,不仅可以去除灰尘和顽固污渍,还能够充分吸收液体状污垢和粘腻的污垢,同时用水擦拭。 只需一次擦拭即可完成,无需花费功夫,节省维护时间。 将床打磨成闪亮状态。 适用于时短和家务效率的理想家电。 一个人生活的最佳选择。
-【吸力+擦拭*2in1一体式吸尘器】"JONR ED12 Lite"是一款可同时吸&amp;擦拭水分的2in1无线直立式吸尘器设计的创意产品。 基于人体工程学的手柄和下重心设计,无需复杂操作的直观操作。 老年人也可放心使用! 长时间使用手腕也不易疲劳的设计。 滚轮刷延伸至前方,自走式,墙壁和桌腿周围,家具的缝隙也能彻底清洁干净。 17,000 Pa的强力吸力,可同时使用吸尘器和拖把,大幅缩短清洁地板时间。 搭载2600mAh的大容量电池和850毫升的清水罐+450毫升的污水箱,可连续工作45分钟,无需频繁加水。 清洁完毕后请自动清洗滚轮刷。 无需繁琐的打扫后,您可以在忙碌的日常保持家清洁。
-【强大的功能,更放心的清洁】抗菌规格的滚轮刷能够抑制细菌的产生! 电解水生成装置的水箱,就可以期待除菌效果! ,紧贴地板的浮动刮刀能够彻底清除细小的垃圾,实现零擦拭残留。 家人的健康保护家居防护。
-[适用于多种地板 * 各种污垢和垃圾] 不仅可以擦拭水,还可以去除地板面的垃圾和污渍。 适用地板材料:聚氯乙烯地板(聚氯乙烯地板)、榻榻米、瓷砖、大理石、地板等。 适用污渍/垃圾:毛发、液体污垢、土壤、沙子、食物溢出、液体污渍、宠物粗相等。 不用担心宝宝会被食物洒落或宠物毛散落的点心!</t>
+          <t>【高效化每天的清扫! 】日本最轻质 擦拭式吸尘器JONR ED12 Lite是一款能更轻松地享受日常清扫,短时间设计新颖创意的吸力&amp;擦拭水2合1无绳吸尘器。 除了灰尘和垃圾外,也可以吸附液体的同时,无需费力地清洗地板。 另外,支持150°平打扫,即使是桌子或沙发等较低的空间(15厘米以上)的清扫也不会有压力,非常舒适。 清洁完毕后,滚筒刷自动清洗,无需繁琐的工作,是一款理想的理想选择。</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
+          <t>B0FL2KXDMX</t>
         </is>
       </c>
       <c r="M38" s="12" t="inlineStr">
@@ -15919,13 +15911,13 @@
         </is>
       </c>
       <c r="O38" s="13">
-        <v>160439</v>
+        <v>167978</v>
       </c>
       <c r="P38" s="13">
-        <v>4124</v>
+        <v>1428</v>
       </c>
       <c r="Q38" s="14">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R38" s="15" t="inlineStr">
         <is>
@@ -15934,7 +15926,7 @@
       </c>
       <c r="S38" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T38" s="13"/>
@@ -15946,25 +15938,25 @@
         <v>1</v>
       </c>
       <c r="Z38" s="13">
-        <v>118000</v>
+        <v>99990</v>
       </c>
       <c r="AA38" s="2"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE38" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF38" s="18">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AG38" s="19">
         <v>0</v>
       </c>
       <c r="AH38" s="13">
-        <v>1020</v>
+        <v>781</v>
       </c>
       <c r="AI38" s="14">
         <v>0.84</v>
@@ -15972,11 +15964,11 @@
       <c r="AJ38"/>
       <c r="AK38" s="11" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AL38" s="17">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="AM38" s="11" t="inlineStr">
         <is>
@@ -15987,14 +15979,14 @@
       <c r="AO38" s="11"/>
       <c r="AP38" s="2"/>
       <c r="AQ38" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR38" s="17">
         <v>1</v>
       </c>
       <c r="AS38" s="12" t="inlineStr">
         <is>
-          <t>-公式ストア</t>
+          <t>JONR JP</t>
         </is>
       </c>
       <c r="AT38" s="11" t="inlineStr">
@@ -16009,12 +16001,12 @@
       </c>
       <c r="AV38" s="12" t="inlineStr">
         <is>
-          <t>莆田市 福建 351119 CN</t>
+          <t>孝感市 湖北 432400 CN</t>
         </is>
       </c>
       <c r="AW38" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC</t>
         </is>
       </c>
       <c r="AX38" s="11"/>
@@ -16022,7 +16014,11 @@
       <c r="AZ38" s="11"/>
       <c r="BA38" s="11"/>
       <c r="BB38" s="11"/>
-      <c r="BC38" s="11"/>
+      <c r="BC38" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD38" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16039,38 +16035,38 @@
       <c r="BI38" s="20"/>
       <c r="BJ38" s="20" t="inlineStr">
         <is>
-          <t>3 kg</t>
+          <t>6 Kilograms</t>
         </is>
       </c>
       <c r="BK38" s="20" t="inlineStr">
         <is>
-          <t>3.00 kg</t>
+          <t>6.00 kg</t>
         </is>
       </c>
       <c r="BL38" s="20" t="inlineStr">
         <is>
-          <t>29.6長さ x 26.9幅 x 113.4高さ cm</t>
+          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
         </is>
       </c>
       <c r="BM38" s="20"/>
       <c r="BN38" s="20" t="inlineStr">
         <is>
-          <t>5.96 kg</t>
+          <t>6 kg</t>
         </is>
       </c>
       <c r="BO38" s="20" t="inlineStr">
         <is>
-          <t>5.96 kg</t>
+          <t>6.00 kg</t>
         </is>
       </c>
       <c r="BP38" s="20" t="inlineStr">
         <is>
-          <t>55.4 x 33.7 x 31.2 cm</t>
+          <t>55.1 x 33.6 x 31.2 cm</t>
         </is>
       </c>
       <c r="BQ38" s="20" t="inlineStr">
         <is>
-          <t>55.40 x 33.70 x 31.20 cm</t>
+          <t>55.10 x 33.60 x 31.20 cm</t>
         </is>
       </c>
       <c r="BR38" s="11" t="inlineStr">
@@ -16086,13 +16082,13 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
+          <t>B0FNQZWZ7T</t>
         </is>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>品牌: JONR | 特殊功能: 干湿两用, 无线, 自行驶式, 轻巧, 轻量级 | 筛选类型: 滤网 | 推荐表面: 硬地板 | 电源: 电池供电</t>
+          <t>品牌: JONR | 特殊功能: HEPA, 可充电, 干湿两用, 无绳, 轻巧 | 筛选类型: HEPA滤网 | 推荐表面: 所有楼面 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -16102,32 +16098,36 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FNQZWZ7T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
+          <t>掃除機 JONR H2 Pro 水拭き掃除機 乾湿両用 高性能 除菌 20000Pa強力吸引 最大45分間連続稼働 モップ自動洗浄＆乾燥機能付き 熱風 コードレス掃除機 180°フラット スティッククリーナー 大容量水タンク 省力デザイン 自立&amp;自走式 両側エッジクリーニング LED表示画面 音声ガイド 家庭用 様々な床材に対応 最大24ヶ月保証</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>【高效化每天的清扫! 】日本最轻质 擦拭式吸尘器JONR ED12 Lite是一款能更轻松地享受日常清扫,短时间设计新颖创意的吸力&amp;擦拭水2合1无绳吸尘器。 除了灰尘和垃圾外,也可以吸附液体的同时,无需费力地清洗地板。 另外,支持150°平打扫,即使是桌子或沙发等较低的空间(15厘米以上)的清扫也不会有压力,非常舒适。 清洁完毕后,滚筒刷自动清洗,无需繁琐的工作,是一款理想的理想选择。</t>
+          <t>【固液分离・防臭设计】业界首个的"底面水箱+可生物降解性单向垃圾袋"双重系统是它的核心。 创新设计的短缩风路抑制污水逆流,阻隔85%以下风道残留水分。 防止内部滋生细菌和霉菌的99%以上,将令人讨厌的生干臭降低到原来约1/3。 进一步支持这个卫生管理,是99.5%的高精度固体分离。 小袋可堵住固体垃圾,水箱内部始终保持清洁。 只需取出垃圾袋,就能实现30秒完全不触摸。 并且,全部保持清洁,IPX6完全防水设计。 因为可以直接水洗包括马达部分的头部,即使是宠物的脱毛或在意头屑的家庭,总是在"开封时"保持相同的清洁。 消除了传统的颤音,新一代卫生管理标准。
+【180°完全倒立也能充满吸力】擦拭式吸尘器H2 PRO可以完全倒立180°的完全倒立。 这款角度也不会降低吸力的设计,自由进入床和沙发等较低的家具下方(间隙约11cm),传统150°设计款式无法到达的"低死角"。 此外,采用左右两侧的墙壁间零距离触摸设计。 由于可以紧密地贴合这个凹槽和家具的腿部,消除边角的清洁漏气。 一次过渡覆盖整个地板,垃圾残留量在0.01g以下,实现了彻底清洁。 支持强力清洁性能,25,000 Pa的吸力和高速旋转的刷子。 由此,达到85%以上的高污水回收率,干固的咖啡污渍等,只需一次去除99.3%。 几乎不残留水痕迹,保证干净清爽的外观。 请一定要试试一下这款"三重解决顽固污渍——这些问题吧。
+【一站式擦拭广阔的家用水擦拭】H2 PRO设计成"一次清洁宽敞的住宅"。 通过最大可连续工作50分钟的大容量储水箱,300平米有限,节省充电和补充,仅需一次即可完成用水擦拭清洁。 这个"让日常的家务更轻,更快、更快乐"的新理念,凝缩了令人惊讶的身材。 双重梳子(双重梳子)结构能够有效消除毛发缠绕,40个立体定压喷射孔自动清洁系统,在清扫的同时保持滚轮保持清洁,保持最佳性能。 小巧的充电支架,只需插入即可立即充电。 内置的65°C高温水路+滚筒高温清洗+高速温风干燥的3档系统,通过刷子两方向旋转来降低含水率。 发挥99.2%的除臭效果,只需擦拭即可实现清洁且干爽无臭的地板。
+【一口就完成家地板的清扫一下】这一台,集合了"吸水、擦拭、水回"这3道工序。 以前需要用吸尘器吸取,下一次拖把,最后将水桶丢进水中,H2 Pro只要一口气通通贯就可以了。 从面包屑到溢出的饮料,干湿两边的垃圾即刻处理。 通过4个迷你辅助轮产生的360°的全方向驱动,复杂的室内布局也能轻松移动。 只需将手腕扭动一下65°,就能让小桌或椅子腿之间滑动缝合,浮现以往吸尘器所没有的"真死角"。 除了机身的轻量化之外,还优化了辅助前进的自走力。 实际操作时手感的重量减轻了惊人的约750克(500毫升的塑料瓶半左右)。 不仅是女性,孩子的手也不会负担,老年人也能轻松单手操作。 从客厅到厨房、卧室,清洁家中也不会觉得手腕和手腕。
+【24小时客户支持】包装内容:擦拭吸尘器×1、收纳支架×1、清洁刷套装×1、带专用清洁液×1、适配器×1、日语使用说明书×1。 还附有"1年商品保修"和"24小时在线支持"。 购买后1年内,对应初始故障和故障。 有什么问题可以随时在24小时内在线咨询。 咨询方法:账户服务的"账户服务"→"订单记录"→"销售者"→"问题"欢迎咨询。 即使长时间使用也很放心,家人也很喜欢。</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FNQZWZ7T?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31Mn69YoVgL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
+          <t>B0FNQZWZ7T</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
@@ -16141,13 +16141,11 @@
         </is>
       </c>
       <c r="O39" s="13">
-        <v>167978</v>
-      </c>
-      <c r="P39" s="13">
-        <v>1428</v>
-      </c>
+        <v>184831</v>
+      </c>
+      <c r="P39" s="13"/>
       <c r="Q39" s="14">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R39" s="15" t="inlineStr">
         <is>
@@ -16156,7 +16154,7 @@
       </c>
       <c r="S39" s="16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T39" s="13"/>
@@ -16167,39 +16165,27 @@
       <c r="Y39" s="17">
         <v>1</v>
       </c>
-      <c r="Z39" s="13">
-        <v>99990</v>
-      </c>
+      <c r="Z39" s="13"/>
       <c r="AA39" s="2"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="17">
-        <v>27</v>
-      </c>
-      <c r="AE39" s="13">
-        <v>5</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="AE39" s="13"/>
       <c r="AF39" s="18">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AG39" s="19">
         <v>0</v>
       </c>
-      <c r="AH39" s="13">
-        <v>781</v>
-      </c>
+      <c r="AH39" s="13"/>
       <c r="AI39" s="14">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AJ39"/>
-      <c r="AK39" s="11" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AL39" s="17">
-        <v>419</v>
-      </c>
+      <c r="AK39" s="11"/>
+      <c r="AL39" s="17"/>
       <c r="AM39" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -16208,52 +16194,24 @@
       <c r="AN39" s="11"/>
       <c r="AO39" s="11"/>
       <c r="AP39" s="2"/>
-      <c r="AQ39" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR39" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS39" s="12" t="inlineStr">
-        <is>
-          <t>JONR JP</t>
-        </is>
-      </c>
+      <c r="AQ39" s="17"/>
+      <c r="AR39" s="17"/>
+      <c r="AS39" s="12"/>
       <c r="AT39" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU39" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV39" s="12" t="inlineStr">
-        <is>
-          <t>孝感市 湖北 432400 CN</t>
-        </is>
-      </c>
-      <c r="AW39" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC</t>
-        </is>
-      </c>
+      <c r="AU39" s="11"/>
+      <c r="AV39" s="12"/>
+      <c r="AW39" s="11"/>
       <c r="AX39" s="11"/>
       <c r="AY39" s="11"/>
       <c r="AZ39" s="11"/>
       <c r="BA39" s="11"/>
       <c r="BB39" s="11"/>
-      <c r="BC39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC39" s="11"/>
+      <c r="BD39" s="11"/>
       <c r="BE39" s="11"/>
       <c r="BF39" s="11" t="inlineStr">
         <is>
@@ -16263,47 +16221,15 @@
       <c r="BG39" s="11"/>
       <c r="BH39" s="12"/>
       <c r="BI39" s="20"/>
-      <c r="BJ39" s="20" t="inlineStr">
-        <is>
-          <t>6 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK39" s="20" t="inlineStr">
-        <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BL39" s="20" t="inlineStr">
-        <is>
-          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ39" s="20"/>
+      <c r="BK39" s="20"/>
+      <c r="BL39" s="20"/>
       <c r="BM39" s="20"/>
-      <c r="BN39" s="20" t="inlineStr">
-        <is>
-          <t>6 kg</t>
-        </is>
-      </c>
-      <c r="BO39" s="20" t="inlineStr">
-        <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BP39" s="20" t="inlineStr">
-        <is>
-          <t>55.1 x 33.6 x 31.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ39" s="20" t="inlineStr">
-        <is>
-          <t>55.10 x 33.60 x 31.20 cm</t>
-        </is>
-      </c>
-      <c r="BR39" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN39" s="20"/>
+      <c r="BO39" s="20"/>
+      <c r="BP39" s="20"/>
+      <c r="BQ39" s="20"/>
+      <c r="BR39" s="11"/>
     </row>
     <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
@@ -16312,52 +16238,53 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0FNQZWZ7T</t>
+          <t>B0FPXLZSWP</t>
         </is>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>品牌: JONR | 特殊功能: HEPA, 可充电, 干湿两用, 无绳, 轻巧 | 筛选类型: HEPA滤网 | 推荐表面: 所有楼面 | 电源: 电池供电</t>
+          <t>品牌: NARWAL | 特殊功能: 干湿两用 | 筛选类型: HEPA滤网 | 推荐表面: 所有楼面 | 电源: 电池供电</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>JONR</t>
+          <t>NARWAL</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FNQZWZ7T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>掃除機 JONR H2 Pro 水拭き掃除機 乾湿両用 高性能 除菌 20000Pa強力吸引 最大45分間連続稼働 モップ自動洗浄＆乾燥機能付き 熱風 コードレス掃除機 180°フラット スティッククリーナー 大容量水タンク 省力デザイン 自立&amp;自走式 両側エッジクリーニング LED表示画面 音声ガイド 家庭用 様々な床材に対応 最大24ヶ月保証</t>
+          <t>Narwal S30 无线擦地吸尘器 20,000Pa吸力 一次性垃圾网</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>【固液分离・防臭设计】业界首个的"底面水箱+可生物降解性单向垃圾袋"双重系统是它的核心。 创新设计的短缩风路抑制污水逆流,阻隔85%以下风道残留水分。 防止内部滋生细菌和霉菌的99%以上,将令人讨厌的生干臭降低到原来约1/3。 进一步支持这个卫生管理,是99.5%的高精度固体分离。 小袋可堵住固体垃圾,水箱内部始终保持清洁。 只需取出垃圾袋,就能实现30秒完全不触摸。 并且,全部保持清洁,IPX6完全防水设计。 因为可以直接水洗包括马达部分的头部,即使是宠物的脱毛或在意头屑的家庭,总是在"开封时"保持相同的清洁。 消除了传统的颤音,新一代卫生管理标准。
-【180°完全倒立也能充满吸力】擦拭式吸尘器H2 PRO可以完全倒立180°的完全倒立。 这款角度也不会降低吸力的设计,自由进入床和沙发等较低的家具下方(间隙约11cm),传统150°设计款式无法到达的"低死角"。 此外,采用左右两侧的墙壁间零距离触摸设计。 由于可以紧密地贴合这个凹槽和家具的腿部,消除边角的清洁漏气。 一次过渡覆盖整个地板,垃圾残留量在0.01g以下,实现了彻底清洁。 支持强力清洁性能,25,000 Pa的吸力和高速旋转的刷子。 由此,达到85%以上的高污水回收率,干固的咖啡污渍等,只需一次去除99.3%。 几乎不残留水痕迹,保证干净清爽的外观。 请一定要试试一下这款"三重解决顽固污渍——这些问题吧。
-【一站式擦拭广阔的家用水擦拭】H2 PRO设计成"一次清洁宽敞的住宅"。 通过最大可连续工作50分钟的大容量储水箱,300平米有限,节省充电和补充,仅需一次即可完成用水擦拭清洁。 这个"让日常的家务更轻,更快、更快乐"的新理念,凝缩了令人惊讶的身材。 双重梳子(双重梳子)结构能够有效消除毛发缠绕,40个立体定压喷射孔自动清洁系统,在清扫的同时保持滚轮保持清洁,保持最佳性能。 小巧的充电支架,只需插入即可立即充电。 内置的65°C高温水路+滚筒高温清洗+高速温风干燥的3档系统,通过刷子两方向旋转来降低含水率。 发挥99.2%的除臭效果,只需擦拭即可实现清洁且干爽无臭的地板。
-【一口就完成家地板的清扫一下】这一台,集合了"吸水、擦拭、水回"这3道工序。 以前需要用吸尘器吸取,下一次拖把,最后将水桶丢进水中,H2 Pro只要一口气通通贯就可以了。 从面包屑到溢出的饮料,干湿两边的垃圾即刻处理。 通过4个迷你辅助轮产生的360°的全方向驱动,复杂的室内布局也能轻松移动。 只需将手腕扭动一下65°,就能让小桌或椅子腿之间滑动缝合,浮现以往吸尘器所没有的"真死角"。 除了机身的轻量化之外,还优化了辅助前进的自走力。 实际操作时手感的重量减轻了惊人的约750克(500毫升的塑料瓶半左右)。 不仅是女性,孩子的手也不会负担,老年人也能轻松单手操作。 从客厅到厨房、卧室,清洁家中也不会觉得手腕和手腕。
-【24小时客户支持】包装内容:擦拭吸尘器×1、收纳支架×1、清洁刷套装×1、带专用清洁液×1、适配器×1、日语使用说明书×1。 还附有"1年商品保修"和"24小时在线支持"。 购买后1年内,对应初始故障和故障。 有什么问题可以随时在24小时内在线咨询。 咨询方法:账户服务的"账户服务"→"订单记录"→"销售者"→"问题"欢迎咨询。 即使长时间使用也很放心,家人也很喜欢。</t>
+          <t>[干垃圾和水分污垢也能彻底清洁] S30 无线吸尘器 湿两用,可擦拭湿的果汁或洒出的意大利面。 20,000Pa的吸力和20N(2kg)的下向压力同时进行吸力和擦水,使所有污垢都闪闪发光。
+[一键式自清洁] S30 吸尘器 无线 带水擦拭的滚轮拖把可以牢固地清洁80℃的温水*,并通过反向旋转彻底清洁拖把。 热熨斗均匀干燥滚轮,在保持蓬松干净的同时,管道和过滤器也会同时干燥。 *使用另售的清洁液(稀释型),可以获得更强大的清洁效果。
+[简单而干净的垃圾处理] 告别繁琐的垃圾处理。 S30 擦水吸尘器 自走式采用一次性垃圾分类网。 不会触摸垃圾或弄脏手。 由于将固体垃圾和污水分开,因此清洁比以往更轻松、更清洁。
+【双梳,零缠结】滚轮部分内置的双梳子可以直接释放地板上的所有头发和绒毛,因此头发不会缠绕在卷筒上。 无需用手取出刷子缠绕的头发。
+【180° 扁平结构&amp;63°头部旋转】一体式S30 擦水吸尘器 无线 自动清洁,采用180°扁平结构,可以顺利进入家具下方或难以到达的地方。 此外,只需手腕的力量即可旋转63°,像桌子腿周围的复杂地形一样,可以轻松清洁每个角落。
+注意:本产品及相关服务的使用仅限日本国内。</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FNQZWZ7T?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31Mn69YoVgL._AC_US200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0FNQZWZ7T</t>
+          <t>B0FPXLZSWP</t>
         </is>
       </c>
       <c r="M40" s="12" t="inlineStr">
@@ -16371,11 +16298,13 @@
         </is>
       </c>
       <c r="O40" s="13">
-        <v>184831</v>
-      </c>
-      <c r="P40" s="13"/>
+        <v>160122</v>
+      </c>
+      <c r="P40" s="13">
+        <v>2593</v>
+      </c>
       <c r="Q40" s="14">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R40" s="15" t="inlineStr">
         <is>
@@ -16384,52 +16313,74 @@
       </c>
       <c r="S40" s="16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T40" s="13"/>
-      <c r="U40" s="14"/>
+      <c r="U40" s="14">
+        <v>-0.78</v>
+      </c>
       <c r="V40" s="13"/>
       <c r="W40" s="13"/>
       <c r="X40" s="13"/>
       <c r="Y40" s="17">
         <v>1</v>
       </c>
-      <c r="Z40" s="13"/>
+      <c r="Z40" s="13">
+        <v>349</v>
+      </c>
       <c r="AA40" s="2"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="17">
-        <v>19</v>
-      </c>
-      <c r="AE40" s="13"/>
+        <v>41</v>
+      </c>
+      <c r="AE40" s="13">
+        <v>0</v>
+      </c>
       <c r="AF40" s="18">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AG40" s="19">
         <v>0</v>
       </c>
-      <c r="AH40" s="13"/>
+      <c r="AH40" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI40" s="14">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AJ40"/>
-      <c r="AK40" s="11"/>
-      <c r="AL40" s="17"/>
+      <c r="AK40" s="11" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AL40" s="17">
+        <v>367</v>
+      </c>
       <c r="AM40" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN40" s="11"/>
       <c r="AO40" s="11"/>
       <c r="AP40" s="2"/>
-      <c r="AQ40" s="17"/>
-      <c r="AR40" s="17"/>
-      <c r="AS40" s="12"/>
+      <c r="AQ40" s="17">
+        <v>9</v>
+      </c>
+      <c r="AR40" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS40" s="12" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="AT40" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AU40" s="11"/>
@@ -16440,8 +16391,16 @@
       <c r="AZ40" s="11"/>
       <c r="BA40" s="11"/>
       <c r="BB40" s="11"/>
-      <c r="BC40" s="11"/>
-      <c r="BD40" s="11"/>
+      <c r="BC40" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD40" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE40" s="11"/>
       <c r="BF40" s="11" t="inlineStr">
         <is>
@@ -16451,15 +16410,47 @@
       <c r="BG40" s="11"/>
       <c r="BH40" s="12"/>
       <c r="BI40" s="20"/>
-      <c r="BJ40" s="20"/>
-      <c r="BK40" s="20"/>
-      <c r="BL40" s="20"/>
+      <c r="BJ40" s="20" t="inlineStr">
+        <is>
+          <t>8 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK40" s="20" t="inlineStr">
+        <is>
+          <t>8.00 kg</t>
+        </is>
+      </c>
+      <c r="BL40" s="20" t="inlineStr">
+        <is>
+          <t>30長さ x 27.1幅 x 22.5高さ cm</t>
+        </is>
+      </c>
       <c r="BM40" s="20"/>
-      <c r="BN40" s="20"/>
-      <c r="BO40" s="20"/>
-      <c r="BP40" s="20"/>
-      <c r="BQ40" s="20"/>
-      <c r="BR40" s="11"/>
+      <c r="BN40" s="20" t="inlineStr">
+        <is>
+          <t>8 kg</t>
+        </is>
+      </c>
+      <c r="BO40" s="20" t="inlineStr">
+        <is>
+          <t>8.00 kg</t>
+        </is>
+      </c>
+      <c r="BP40" s="20" t="inlineStr">
+        <is>
+          <t>74 x 35 x 29 cm</t>
+        </is>
+      </c>
+      <c r="BQ40" s="20" t="inlineStr">
+        <is>
+          <t>74.00 x 35.00 x 29.00 cm</t>
+        </is>
+      </c>
+      <c r="BR40" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
@@ -16468,53 +16459,45 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
+          <t>B0H5WDMCLX</t>
         </is>
       </c>
       <c r="D41" s="12"/>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>品牌: NARWAL | 特殊功能: 干湿两用 | 筛选类型: HEPA滤网 | 推荐表面: 所有楼面 | 电源: 电池供电</t>
-        </is>
-      </c>
+      <c r="E41" s="12"/>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>NARWAL</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H5WDMCLX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Narwal S30 无线擦地吸尘器 20,000Pa吸力 一次性垃圾网</t>
+          <t>dreame H12 Pro FlexReach 擦水吸尘器与替换用过滤器 套装</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>[干垃圾和水分污垢也能彻底清洁] S30 无线吸尘器 湿两用,可擦拭湿的果汁或洒出的意大利面。 20,000Pa的吸力和20N(2kg)的下向压力同时进行吸力和擦水,使所有污垢都闪闪发光。
-[一键式自清洁] S30 吸尘器 无线 带水擦拭的滚轮拖把可以牢固地清洁80℃的温水*,并通过反向旋转彻底清洁拖把。 热熨斗均匀干燥滚轮,在保持蓬松干净的同时,管道和过滤器也会同时干燥。 *使用另售的清洁液(稀释型),可以获得更强大的清洁效果。
-[简单而干净的垃圾处理] 告别繁琐的垃圾处理。 S30 擦水吸尘器 自走式采用一次性垃圾分类网。 不会触摸垃圾或弄脏手。 由于将固体垃圾和污水分开,因此清洁比以往更轻松、更清洁。
-【双梳,零缠结】滚轮部分内置的双梳子可以直接释放地板上的所有头发和绒毛,因此头发不会缠绕在卷筒上。 无需用手取出刷子缠绕的头发。
-【180° 扁平结构&amp;63°头部旋转】一体式S30 擦水吸尘器 无线 自动清洁,采用180°扁平结构,可以顺利进入家具下方或难以到达的地方。 此外,只需手腕的力量即可旋转63°,像桌子腿周围的复杂地形一样,可以轻松清洁每个角落。
-注意:本产品及相关服务的使用仅限日本国内。</t>
+          <t>【强力干湿两用吸尘器】 具备18,000 Pa强大吸力的dreame H12 Pro FlexReach水擦拭吸尘器,可以同时吸尘和水擦拭,因此可以快速清除湿污垢的干燥污垢。 彻底缩短清洁地板的时间,每一次的完成都更加美观。
+Dreame 水擦拭吸尘器滤芯 (1 件装) G10 / H12 Pro / H12 Dual / H12S / H12 Pro FlexReach / H12 Dual FlexReach / H15S 替换过滤器</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31ZGQqLBLNL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
+          <t>B0H5WDMCLX</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
@@ -16528,13 +16511,11 @@
         </is>
       </c>
       <c r="O41" s="13">
-        <v>160122</v>
-      </c>
-      <c r="P41" s="13">
-        <v>2593</v>
-      </c>
+        <v>129425</v>
+      </c>
+      <c r="P41" s="13"/>
       <c r="Q41" s="14">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R41" s="15" t="inlineStr">
         <is>
@@ -16543,74 +16524,48 @@
       </c>
       <c r="S41" s="16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T41" s="13"/>
-      <c r="U41" s="14">
-        <v>-0.78</v>
-      </c>
+      <c r="U41" s="14"/>
       <c r="V41" s="13"/>
       <c r="W41" s="13"/>
       <c r="X41" s="13"/>
       <c r="Y41" s="17">
         <v>1</v>
       </c>
-      <c r="Z41" s="13">
-        <v>349</v>
-      </c>
+      <c r="Z41" s="13"/>
       <c r="AA41" s="2"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="2"/>
-      <c r="AD41" s="17">
-        <v>41</v>
-      </c>
-      <c r="AE41" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="18">
-        <v>3.6</v>
-      </c>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="13"/>
+      <c r="AF41" s="18"/>
       <c r="AG41" s="19">
         <v>0</v>
       </c>
-      <c r="AH41" s="13">
-        <v>1020</v>
-      </c>
+      <c r="AH41" s="13"/>
       <c r="AI41" s="14">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="AJ41"/>
-      <c r="AK41" s="11" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AL41" s="17">
-        <v>367</v>
-      </c>
+      <c r="AK41" s="11"/>
+      <c r="AL41" s="17"/>
       <c r="AM41" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN41" s="11"/>
       <c r="AO41" s="11"/>
       <c r="AP41" s="2"/>
-      <c r="AQ41" s="17">
-        <v>9</v>
-      </c>
-      <c r="AR41" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS41" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="AQ41" s="17"/>
+      <c r="AR41" s="17"/>
+      <c r="AS41" s="12"/>
       <c r="AT41" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU41" s="11"/>
@@ -16621,66 +16576,22 @@
       <c r="AZ41" s="11"/>
       <c r="BA41" s="11"/>
       <c r="BB41" s="11"/>
-      <c r="BC41" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD41" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC41" s="11"/>
+      <c r="BD41" s="11"/>
       <c r="BE41" s="11"/>
-      <c r="BF41" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF41" s="11"/>
       <c r="BG41" s="11"/>
       <c r="BH41" s="12"/>
       <c r="BI41" s="20"/>
-      <c r="BJ41" s="20" t="inlineStr">
-        <is>
-          <t>8 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK41" s="20" t="inlineStr">
-        <is>
-          <t>8.00 kg</t>
-        </is>
-      </c>
-      <c r="BL41" s="20" t="inlineStr">
-        <is>
-          <t>30長さ x 27.1幅 x 22.5高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ41" s="20"/>
+      <c r="BK41" s="20"/>
+      <c r="BL41" s="20"/>
       <c r="BM41" s="20"/>
-      <c r="BN41" s="20" t="inlineStr">
-        <is>
-          <t>8 kg</t>
-        </is>
-      </c>
-      <c r="BO41" s="20" t="inlineStr">
-        <is>
-          <t>8.00 kg</t>
-        </is>
-      </c>
-      <c r="BP41" s="20" t="inlineStr">
-        <is>
-          <t>74 x 35 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BQ41" s="20" t="inlineStr">
-        <is>
-          <t>74.00 x 35.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BR41" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN41" s="20"/>
+      <c r="BO41" s="20"/>
+      <c r="BP41" s="20"/>
+      <c r="BQ41" s="20"/>
+      <c r="BR41" s="11"/>
     </row>
     <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
@@ -16689,45 +16600,52 @@
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>B0H5WDMCLX</t>
+          <t>B0HHN8HTLL</t>
         </is>
       </c>
       <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>品牌: Dyson | 特殊功能: コードレス | 推荐表面: ハードフロア、カーペット、布団、車内 | 电源: バッテリー式 | 随附部件: Fluffy Optic™クリーナーヘッド</t>
+        </is>
+      </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H5WDMCLX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>dreame H12 Pro FlexReach 擦水吸尘器与替换用过滤器 套装</t>
+          <t>Dyson(ダイソン) Dyson V12 Detect Slim Fluffyコードレススティック掃除機 ダイソン公式限定 延長保証1年モデル</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>【强力干湿两用吸尘器】 具备18,000 Pa强大吸力的dreame H12 Pro FlexReach水擦拭吸尘器,可以同时吸尘和水擦拭,因此可以快速清除湿污垢的干燥污垢。 彻底缩短清洁地板的时间,每一次的完成都更加美观。
-Dreame 水擦拭吸尘器滤芯 (1 件装) G10 / H12 Pro / H12 Dual / H12S / H12 Pro FlexReach / H12 Dual FlexReach / H15S 替换过滤器</t>
+          <t>【メーカー保証の有効化】製品登録をしていただくと、2年間のメーカー保証が有効になります。「ダイソン 製品保証登録」で検索し、ダイソン公式サイトから製品登録を行なってください。
+本製品にはUpCare延長保証サービスによる1年間の延長保証が設定されています。延長保証サービスの適用条件については、購入時の保証内容をご確認ください。
+【延長保証書の発行】本製品のご購入後に延長保証の保証書が発行されます。保証書発行時に「延長保証加入受付メール」をお送りいたしますので、メールの記載にしたがって、お客様の延長保証書を確認してください。なお、紙の保証書は製品に同封されません。
+【メールが届かない場合】お客様のメール受信設定上、延長保証加入受付メールが届かない場合は、「UpCare」で検索し、UpCare公式サイトから延長保証書をご確認ください。
+【延長保証対応範囲】通常のメーカー保証期間（2年間）終了後も、自然故障を1年間まで無償で修理・交換いたします。※落下や水濡れによる故障や消耗品の劣化は対象外となりますので、あらかじめご了承ください。</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31ZGQqLBLNL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/318dht38dBL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0H5WDMCLX</t>
+          <t>B0HHN8HTLL</t>
         </is>
       </c>
       <c r="M42" s="12" t="inlineStr">
@@ -16741,7 +16659,7 @@
         </is>
       </c>
       <c r="O42" s="13">
-        <v>129425</v>
+        <v>134558</v>
       </c>
       <c r="P42" s="13"/>
       <c r="Q42" s="14">
@@ -16754,7 +16672,7 @@
       </c>
       <c r="S42" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T42" s="13"/>
@@ -16813,7 +16731,11 @@
       <c r="BG42" s="11"/>
       <c r="BH42" s="12"/>
       <c r="BI42" s="20"/>
-      <c r="BJ42" s="20"/>
+      <c r="BJ42" s="20" t="inlineStr">
+        <is>
+          <t>3.2 千克</t>
+        </is>
+      </c>
       <c r="BK42" s="20"/>
       <c r="BL42" s="20"/>
       <c r="BM42" s="20"/>
@@ -16830,52 +16752,51 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0HHN8HTLL</t>
+          <t>B0HK3VZRJP</t>
         </is>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>品牌: Dyson | 特殊功能: コードレス | 推荐表面: ハードフロア、カーペット、布団、車内 | 电源: バッテリー式 | 随附部件: Fluffy Optic™クリーナーヘッド</t>
+          <t>品牌: Generic | 特殊功能: コンパクト, 軽量 | 筛选类型: ディスク | 推荐表面: フローリング | 电源: 電源コード式</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Generic</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) Dyson V12 Detect Slim Fluffyコードレススティック掃除機 ダイソン公式限定 延長保証1年モデル</t>
+          <t>キャニスター掃除機 コード式サイクロン 吸込仕事率 450W パワフル吸引 お手入れ簡単 ベージュ</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>【メーカー保証の有効化】製品登録をしていただくと、2年間のメーカー保証が有効になります。「ダイソン 製品保証登録」で検索し、ダイソン公式サイトから製品登録を行なってください。
-本製品にはUpCare延長保証サービスによる1年間の延長保証が設定されています。延長保証サービスの適用条件については、購入時の保証内容をご確認ください。
-【延長保証書の発行】本製品のご購入後に延長保証の保証書が発行されます。保証書発行時に「延長保証加入受付メール」をお送りいたしますので、メールの記載にしたがって、お客様の延長保証書を確認してください。なお、紙の保証書は製品に同封されません。
-【メールが届かない場合】お客様のメール受信設定上、延長保証加入受付メールが届かない場合は、「UpCare」で検索し、UpCare公式サイトから延長保証書をご確認ください。
-【延長保証対応範囲】通常のメーカー保証期間（2年間）終了後も、自然故障を1年間まで無償で修理・交換いたします。※落下や水濡れによる故障や消耗品の劣化は対象外となりますので、あらかじめご了承ください。</t>
+          <t>✅吸込仕事率(※1):290W～約80W
+✅運転音(※2):63dB～約58dB
+✅本体質量(※2):2.2kg
+ABS 樹脂製で丈夫、運転音を抑えた設計で騒音が気になる時間帯でも使いやすい</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HK3VZRJP?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/318dht38dBL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31t8FaM3RmL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0HHN8HTLL</t>
+          <t>B0HK3VZRJP</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
@@ -16889,7 +16810,7 @@
         </is>
       </c>
       <c r="O43" s="13">
-        <v>134558</v>
+        <v>113316</v>
       </c>
       <c r="P43" s="13"/>
       <c r="Q43" s="14">
@@ -16902,7 +16823,7 @@
       </c>
       <c r="S43" s="16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T43" s="13"/>
@@ -16963,7 +16884,7 @@
       <c r="BI43" s="20"/>
       <c r="BJ43" s="20" t="inlineStr">
         <is>
-          <t>3.2 千克</t>
+          <t>2.2 千克</t>
         </is>
       </c>
       <c r="BK43" s="20"/>
@@ -16974,157 +16895,6 @@
       <c r="BP43" s="20"/>
       <c r="BQ43" s="20"/>
       <c r="BR43" s="11"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <v>43</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>B0HK3VZRJP</t>
-        </is>
-      </c>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Generic | 特殊功能: コンパクト, 軽量 | 筛选类型: ディスク | 推荐表面: フローリング | 电源: 電源コード式</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Generic</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>キャニスター掃除機 コード式サイクロン 吸込仕事率 450W パワフル吸引 お手入れ簡単 ベージュ</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>✅吸込仕事率(※1):290W～約80W
-✅運転音(※2):63dB～約58dB
-✅本体質量(※2):2.2kg
-ABS 樹脂製で丈夫、運転音を抑えた設計で騒音が気になる時間帯でも使いやすい</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HK3VZRJP?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31t8FaM3RmL._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>B0HK3VZRJP</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="inlineStr">
-        <is>
-          <t>家装及园艺:电动工具:商用干湿两用吸尘器</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>家装及园艺</t>
-        </is>
-      </c>
-      <c r="O44" s="13">
-        <v>113316</v>
-      </c>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="14">
-        <v>0</v>
-      </c>
-      <c r="R44" s="15" t="inlineStr">
-        <is>
-          <t>商用干湿两用吸尘器</t>
-        </is>
-      </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="T44" s="13"/>
-      <c r="U44" s="14"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="13"/>
-      <c r="AA44" s="2"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="17"/>
-      <c r="AE44" s="13"/>
-      <c r="AF44" s="18"/>
-      <c r="AG44" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="13"/>
-      <c r="AI44" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="11"/>
-      <c r="AL44" s="17"/>
-      <c r="AM44" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN44" s="11"/>
-      <c r="AO44" s="11"/>
-      <c r="AP44" s="2"/>
-      <c r="AQ44" s="17"/>
-      <c r="AR44" s="17"/>
-      <c r="AS44" s="12"/>
-      <c r="AT44" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU44" s="11"/>
-      <c r="AV44" s="12"/>
-      <c r="AW44" s="11"/>
-      <c r="AX44" s="11"/>
-      <c r="AY44" s="11"/>
-      <c r="AZ44" s="11"/>
-      <c r="BA44" s="11"/>
-      <c r="BB44" s="11"/>
-      <c r="BC44" s="11"/>
-      <c r="BD44" s="11"/>
-      <c r="BE44" s="11"/>
-      <c r="BF44" s="11"/>
-      <c r="BG44" s="11"/>
-      <c r="BH44" s="12"/>
-      <c r="BI44" s="20"/>
-      <c r="BJ44" s="20" t="inlineStr">
-        <is>
-          <t>2.2 千克</t>
-        </is>
-      </c>
-      <c r="BK44" s="20"/>
-      <c r="BL44" s="20"/>
-      <c r="BM44" s="20"/>
-      <c r="BN44" s="20"/>
-      <c r="BO44" s="20"/>
-      <c r="BP44" s="20"/>
-      <c r="BQ44" s="20"/>
-      <c r="BR44" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17326,143 +17096,135 @@
     <hyperlink ref="M26" r:id="rId194" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N26" r:id="rId195"/>
     <hyperlink ref="AW26" r:id="rId196" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU"/>
-    <hyperlink ref="C27" r:id="rId197" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
-    <hyperlink ref="G27" r:id="rId198" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J27" r:id="rId199" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1"/>
-    <hyperlink ref="K27" r:id="rId200" tooltip="https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
+    <hyperlink ref="C27" r:id="rId197" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="G27" r:id="rId198" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J27" r:id="rId199" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
+    <hyperlink ref="K27" r:id="rId200" tooltip="https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
     <hyperlink ref="M27" r:id="rId202" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N27" r:id="rId203"/>
-    <hyperlink ref="AW27" r:id="rId204" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
-    <hyperlink ref="C28" r:id="rId205" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
-    <hyperlink ref="G28" r:id="rId206" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J28" r:id="rId207" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
-    <hyperlink ref="K28" r:id="rId208" tooltip="https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId209" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="AW27" r:id="rId204" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
+    <hyperlink ref="C28" r:id="rId205" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="G28" r:id="rId206" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E"/>
+    <hyperlink ref="J28" r:id="rId207" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
+    <hyperlink ref="K28" r:id="rId208" tooltip="https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg"/>
+    <hyperlink ref="L28" r:id="rId209" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
     <hyperlink ref="M28" r:id="rId210" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N28" r:id="rId211"/>
-    <hyperlink ref="AW28" r:id="rId212" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
-    <hyperlink ref="C29" r:id="rId213" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
-    <hyperlink ref="G29" r:id="rId214" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E"/>
-    <hyperlink ref="J29" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
-    <hyperlink ref="K29" r:id="rId216" tooltip="https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId217" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="AW28" r:id="rId212" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V"/>
+    <hyperlink ref="C29" r:id="rId213" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
+    <hyperlink ref="G29" r:id="rId214" tooltip="https://www.amazon.co.jp/-/zh/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J29" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1"/>
+    <hyperlink ref="K29" r:id="rId216" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId217" tooltip="https://www.amazon.co.jp/dp/B0GXZR4TNN"/>
     <hyperlink ref="M29" r:id="rId218" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N29" r:id="rId219"/>
-    <hyperlink ref="AW29" r:id="rId220" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V"/>
-    <hyperlink ref="C30" r:id="rId221" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
-    <hyperlink ref="G30" r:id="rId222" tooltip="https://www.amazon.co.jp/-/zh/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J30" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1"/>
-    <hyperlink ref="K30" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B0GXZR4TNN"/>
+    <hyperlink ref="AW29" r:id="rId220" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V"/>
+    <hyperlink ref="C30" r:id="rId221" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
+    <hyperlink ref="G30" r:id="rId222" tooltip="https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J30" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
+    <hyperlink ref="K30" r:id="rId224" tooltip="https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
     <hyperlink ref="M30" r:id="rId226" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N30" r:id="rId227"/>
-    <hyperlink ref="AW30" r:id="rId228" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V"/>
-    <hyperlink ref="C31" r:id="rId229" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="G31" r:id="rId230" tooltip="https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId231" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
-    <hyperlink ref="K31" r:id="rId232" tooltip="https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId233" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
+    <hyperlink ref="AW30" r:id="rId228" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
+    <hyperlink ref="C31" r:id="rId229" tooltip="https://www.amazon.co.jp/dp/B004D2ESD6"/>
+    <hyperlink ref="G31" r:id="rId230" tooltip="https://www.amazon.co.jp/-/zh/ラッキーウッド-Luckywood/b/ref=bl_dp_s_web_24383112051?ie=UTF8&amp;node=24383112051&amp;field-lbr_brands_browse-bin=%E3%83%A9%E3%83%83%E3%82%AD%E3%83%BC%E3%82%A6%E3%83%83%E3%83%89%28Luckywood%29"/>
+    <hyperlink ref="J31" r:id="rId231" tooltip="https://www.amazon.co.jp/dp/B004D2ESD6?psc=1"/>
+    <hyperlink ref="K31" r:id="rId232" tooltip="https://m.media-amazon.com/images/I/41rAwhmWDoL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId233" tooltip="https://www.amazon.co.jp/dp/B081F4CR4S"/>
     <hyperlink ref="M31" r:id="rId234" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N31" r:id="rId235"/>
-    <hyperlink ref="AW31" r:id="rId236" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
-    <hyperlink ref="C32" r:id="rId237" tooltip="https://www.amazon.co.jp/dp/B004D2ESD6"/>
-    <hyperlink ref="G32" r:id="rId238" tooltip="https://www.amazon.co.jp/-/zh/ラッキーウッド-Luckywood/b/ref=bl_dp_s_web_24383112051?ie=UTF8&amp;node=24383112051&amp;field-lbr_brands_browse-bin=%E3%83%A9%E3%83%83%E3%82%AD%E3%83%BC%E3%82%A6%E3%83%83%E3%83%89%28Luckywood%29"/>
-    <hyperlink ref="J32" r:id="rId239" tooltip="https://www.amazon.co.jp/dp/B004D2ESD6?psc=1"/>
-    <hyperlink ref="K32" r:id="rId240" tooltip="https://m.media-amazon.com/images/I/41rAwhmWDoL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B081F4CR4S"/>
+    <hyperlink ref="AW31" r:id="rId236" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SBGLLXVMPUPP"/>
+    <hyperlink ref="C32" r:id="rId237" tooltip="https://www.amazon.co.jp/dp/B0183900C2"/>
+    <hyperlink ref="G32" r:id="rId238" tooltip="https://www.amazon.co.jp/-/zh/stores/FUKAI/page/834EE7E8-56E1-4105-8E98-045B52696442?lp_asin=B0183900C2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J32" r:id="rId239" tooltip="https://www.amazon.co.jp/dp/B0183900C2?psc=1"/>
+    <hyperlink ref="K32" r:id="rId240" tooltip="https://m.media-amazon.com/images/I/31ZDf4xaXpL._AC_US200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0183900C2"/>
     <hyperlink ref="M32" r:id="rId242" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N32" r:id="rId243"/>
-    <hyperlink ref="AW32" r:id="rId244" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SBGLLXVMPUPP"/>
-    <hyperlink ref="C33" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0183900C2"/>
-    <hyperlink ref="G33" r:id="rId246" tooltip="https://www.amazon.co.jp/-/zh/stores/FUKAI/page/834EE7E8-56E1-4105-8E98-045B52696442?lp_asin=B0183900C2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J33" r:id="rId247" tooltip="https://www.amazon.co.jp/dp/B0183900C2?psc=1"/>
-    <hyperlink ref="K33" r:id="rId248" tooltip="https://m.media-amazon.com/images/I/31ZDf4xaXpL._AC_US200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId249" tooltip="https://www.amazon.co.jp/dp/B0183900C2"/>
-    <hyperlink ref="M33" r:id="rId250" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N33" r:id="rId251"/>
-    <hyperlink ref="C34" r:id="rId252" tooltip="https://www.amazon.co.jp/dp/B08MDZSSDP"/>
-    <hyperlink ref="G34" r:id="rId253" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=DEKOprojp"/>
-    <hyperlink ref="J34" r:id="rId254" tooltip="https://www.amazon.co.jp/dp/B08MDZSSDP?psc=1"/>
-    <hyperlink ref="K34" r:id="rId255" tooltip="https://m.media-amazon.com/images/I/31rTP7TuVHL._AC_US200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B08RYKLST5"/>
-    <hyperlink ref="M34" r:id="rId257" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N34" r:id="rId258"/>
-    <hyperlink ref="C35" r:id="rId259" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
-    <hyperlink ref="G35" r:id="rId260" tooltip="https://www.amazon.co.jp/-/zh/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln"/>
-    <hyperlink ref="J35" r:id="rId261" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
-    <hyperlink ref="K35" r:id="rId262" tooltip="https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId263" tooltip="https://www.amazon.co.jp/dp/B0CQCGX9DX"/>
+    <hyperlink ref="C33" r:id="rId244" tooltip="https://www.amazon.co.jp/dp/B08MDZSSDP"/>
+    <hyperlink ref="G33" r:id="rId245" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=DEKOprojp"/>
+    <hyperlink ref="J33" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B08MDZSSDP?psc=1"/>
+    <hyperlink ref="K33" r:id="rId247" tooltip="https://m.media-amazon.com/images/I/31rTP7TuVHL._AC_US200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B08RYKLST5"/>
+    <hyperlink ref="M33" r:id="rId249" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N33" r:id="rId250"/>
+    <hyperlink ref="C34" r:id="rId251" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
+    <hyperlink ref="G34" r:id="rId252" tooltip="https://www.amazon.co.jp/-/zh/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln"/>
+    <hyperlink ref="J34" r:id="rId253" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
+    <hyperlink ref="K34" r:id="rId254" tooltip="https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId255" tooltip="https://www.amazon.co.jp/dp/B0CQCGX9DX"/>
+    <hyperlink ref="M34" r:id="rId256" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N34" r:id="rId257"/>
+    <hyperlink ref="AW34" r:id="rId258" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U"/>
+    <hyperlink ref="C35" r:id="rId259" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
+    <hyperlink ref="G35" r:id="rId260" tooltip="https://www.amazon.co.jp/-/zh/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B0CF9P7W51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId261" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
+    <hyperlink ref="K35" r:id="rId262" tooltip="https://m.media-amazon.com/images/I/318f4iR6OhL._AC_US200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId263" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
     <hyperlink ref="M35" r:id="rId264" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N35" r:id="rId265"/>
-    <hyperlink ref="AW35" r:id="rId266" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U"/>
-    <hyperlink ref="C36" r:id="rId267" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="G36" r:id="rId268" tooltip="https://www.amazon.co.jp/-/zh/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B0CF9P7W51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId269" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
-    <hyperlink ref="K36" r:id="rId270" tooltip="https://m.media-amazon.com/images/I/318f4iR6OhL._AC_US200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="M36" r:id="rId272" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N36" r:id="rId273"/>
-    <hyperlink ref="C37" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
-    <hyperlink ref="G37" r:id="rId275" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J37" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1"/>
-    <hyperlink ref="K37" r:id="rId277" tooltip="https://m.media-amazon.com/images/I/31gWtVLKoDL._AC_US200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
-    <hyperlink ref="M37" r:id="rId279" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N37" r:id="rId280"/>
-    <hyperlink ref="C38" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
-    <hyperlink ref="G38" r:id="rId282" tooltip="https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
-    <hyperlink ref="K38" r:id="rId284" tooltip="https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId285" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="C36" r:id="rId266" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
+    <hyperlink ref="G36" r:id="rId267" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J36" r:id="rId268" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1"/>
+    <hyperlink ref="K36" r:id="rId269" tooltip="https://m.media-amazon.com/images/I/31gWtVLKoDL._AC_US200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId270" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
+    <hyperlink ref="M36" r:id="rId271" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N36" r:id="rId272"/>
+    <hyperlink ref="C37" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="G37" r:id="rId274" tooltip="https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId275" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
+    <hyperlink ref="K37" r:id="rId276" tooltip="https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId277" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="M37" r:id="rId278" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N37" r:id="rId279"/>
+    <hyperlink ref="AW37" r:id="rId280" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6"/>
+    <hyperlink ref="C38" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="G38" r:id="rId282" tooltip="https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
+    <hyperlink ref="K38" r:id="rId284" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId285" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
     <hyperlink ref="M38" r:id="rId286" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N38" r:id="rId287"/>
-    <hyperlink ref="AW38" r:id="rId288" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6"/>
-    <hyperlink ref="C39" r:id="rId289" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
-    <hyperlink ref="G39" r:id="rId290" tooltip="https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId291" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
-    <hyperlink ref="K39" r:id="rId292" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId293" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="AW38" r:id="rId288" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC"/>
+    <hyperlink ref="C39" r:id="rId289" tooltip="https://www.amazon.co.jp/dp/B0FNQZWZ7T"/>
+    <hyperlink ref="G39" r:id="rId290" tooltip="https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FNQZWZ7T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId291" tooltip="https://www.amazon.co.jp/dp/B0FNQZWZ7T?psc=1"/>
+    <hyperlink ref="K39" r:id="rId292" tooltip="https://m.media-amazon.com/images/I/31Mn69YoVgL._AC_US200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId293" tooltip="https://www.amazon.co.jp/dp/B0FNQZWZ7T"/>
     <hyperlink ref="M39" r:id="rId294" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N39" r:id="rId295"/>
-    <hyperlink ref="AW39" r:id="rId296" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC"/>
-    <hyperlink ref="C40" r:id="rId297" tooltip="https://www.amazon.co.jp/dp/B0FNQZWZ7T"/>
-    <hyperlink ref="G40" r:id="rId298" tooltip="https://www.amazon.co.jp/-/zh/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FNQZWZ7T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId299" tooltip="https://www.amazon.co.jp/dp/B0FNQZWZ7T?psc=1"/>
-    <hyperlink ref="K40" r:id="rId300" tooltip="https://m.media-amazon.com/images/I/31Mn69YoVgL._AC_US200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId301" tooltip="https://www.amazon.co.jp/dp/B0FNQZWZ7T"/>
-    <hyperlink ref="M40" r:id="rId302" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N40" r:id="rId303"/>
-    <hyperlink ref="C41" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="G41" r:id="rId305" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId306" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
-    <hyperlink ref="K41" r:id="rId307" tooltip="https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId308" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="M41" r:id="rId309" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N41" r:id="rId310"/>
-    <hyperlink ref="C42" r:id="rId311" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
-    <hyperlink ref="G42" r:id="rId312" tooltip="https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H5WDMCLX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId313" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1"/>
-    <hyperlink ref="K42" r:id="rId314" tooltip="https://m.media-amazon.com/images/I/31ZGQqLBLNL._AC_US200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId315" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
-    <hyperlink ref="M42" r:id="rId316" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N42" r:id="rId317"/>
-    <hyperlink ref="C43" r:id="rId318" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
-    <hyperlink ref="G43" r:id="rId319" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J43" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1"/>
-    <hyperlink ref="K43" r:id="rId321" tooltip="https://m.media-amazon.com/images/I/318dht38dBL._AC_US200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId322" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
-    <hyperlink ref="M43" r:id="rId323" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N43" r:id="rId324"/>
-    <hyperlink ref="C44" r:id="rId325" tooltip="https://www.amazon.co.jp/dp/B0HK3VZRJP"/>
-    <hyperlink ref="G44" r:id="rId326" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Generic"/>
-    <hyperlink ref="J44" r:id="rId327" tooltip="https://www.amazon.co.jp/dp/B0HK3VZRJP?psc=1"/>
-    <hyperlink ref="K44" r:id="rId328" tooltip="https://m.media-amazon.com/images/I/31t8FaM3RmL._AC_US200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId329" tooltip="https://www.amazon.co.jp/dp/B0HK3VZRJP"/>
-    <hyperlink ref="M44" r:id="rId330" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N44" r:id="rId331"/>
+    <hyperlink ref="C40" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="G40" r:id="rId297" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId298" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
+    <hyperlink ref="K40" r:id="rId299" tooltip="https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="M40" r:id="rId301" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N40" r:id="rId302"/>
+    <hyperlink ref="C41" r:id="rId303" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
+    <hyperlink ref="G41" r:id="rId304" tooltip="https://www.amazon.co.jp/-/zh/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H5WDMCLX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId305" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1"/>
+    <hyperlink ref="K41" r:id="rId306" tooltip="https://m.media-amazon.com/images/I/31ZGQqLBLNL._AC_US200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId307" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
+    <hyperlink ref="M41" r:id="rId308" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N41" r:id="rId309"/>
+    <hyperlink ref="C42" r:id="rId310" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
+    <hyperlink ref="G42" r:id="rId311" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J42" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1"/>
+    <hyperlink ref="K42" r:id="rId313" tooltip="https://m.media-amazon.com/images/I/318dht38dBL._AC_US200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId314" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
+    <hyperlink ref="M42" r:id="rId315" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N42" r:id="rId316"/>
+    <hyperlink ref="C43" r:id="rId317" tooltip="https://www.amazon.co.jp/dp/B0HK3VZRJP"/>
+    <hyperlink ref="G43" r:id="rId318" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Generic"/>
+    <hyperlink ref="J43" r:id="rId319" tooltip="https://www.amazon.co.jp/dp/B0HK3VZRJP?psc=1"/>
+    <hyperlink ref="K43" r:id="rId320" tooltip="https://m.media-amazon.com/images/I/31t8FaM3RmL._AC_US200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId321" tooltip="https://www.amazon.co.jp/dp/B0HK3VZRJP"/>
+    <hyperlink ref="M43" r:id="rId322" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N43" r:id="rId323"/>
   </hyperlinks>
-  <drawing r:id="rId332"/>
+  <drawing r:id="rId324"/>
 </worksheet>
 </file>
 
@@ -17521,18 +17283,18 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C2" s="13">
-        <v>37749789</v>
+        <v>37569792</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13">
-        <v>61582.03752039152</v>
+        <v>61589.822950819675</v>
       </c>
       <c r="G2" s="19">
-        <v>0.13982664233576642</v>
+        <v>0.1392376169824241</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17553,7 +17315,7 @@
         <v>58640.7520661157</v>
       </c>
       <c r="G3" s="19">
-        <v>0.0552007299270073</v>
+        <v>0.05523853001597809</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17574,7 +17336,7 @@
         <v>22783.0</v>
       </c>
       <c r="G4" s="19">
-        <v>0.10697992700729927</v>
+        <v>0.10705318420451952</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17595,7 +17357,7 @@
         <v>30417.059602649006</v>
       </c>
       <c r="G5" s="19">
-        <v>0.06888686131386862</v>
+        <v>0.06893403332572472</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17616,7 +17378,7 @@
         <v>24300.104529616725</v>
       </c>
       <c r="G6" s="19">
-        <v>0.06546532846715329</v>
+        <v>0.06551015749828806</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17637,7 +17399,7 @@
         <v>3980.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.3759124087591241</v>
+        <v>0.37616982424104084</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17658,7 +17420,7 @@
         <v>59707.73786407767</v>
       </c>
       <c r="G8" s="19">
-        <v>0.023494525547445255</v>
+        <v>0.023510614015065052</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17679,7 +17441,7 @@
         <v>8999.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.07937956204379562</v>
+        <v>0.07943391919653048</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17700,7 +17462,7 @@
         <v>74800.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.005702554744525547</v>
+        <v>0.0057064597123944304</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17721,7 +17483,7 @@
         <v>31879.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.009352189781021899</v>
+        <v>0.009358593928326865</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17742,7 +17504,7 @@
         <v>13204.307692307691</v>
       </c>
       <c r="G12" s="19">
-        <v>0.014826642335766423</v>
+        <v>0.01483679525222552</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17763,7 +17525,7 @@
         <v>58632.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.002052919708029197</v>
+        <v>0.002054325496461995</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17784,7 +17546,7 @@
         <v>15129.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.007527372262773723</v>
+        <v>0.007532526820360649</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17805,7 +17567,7 @@
         <v>6573.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.014598540145985401</v>
+        <v>0.014608536863729742</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17826,7 +17588,7 @@
         <v>11661.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.006386861313868613</v>
+        <v>0.006391234877881762</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17847,7 +17609,7 @@
         <v>7160.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.006843065693430657</v>
+        <v>0.006847751654873316</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17868,7 +17630,7 @@
         <v>4500.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.006843065693430657</v>
+        <v>0.006847751654873316</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17889,7 +17651,7 @@
         <v>687.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.01072080291970803</v>
+        <v>0.01072814425930153</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18040,7 +17802,7 @@
         <v>43795.564423076925</v>
       </c>
       <c r="G2" s="19">
-        <v>0.23722627737226276</v>
+        <v>0.23738872403560832</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18061,7 +17823,7 @@
         <v>58640.7520661157</v>
       </c>
       <c r="G3" s="19">
-        <v>0.0552007299270073</v>
+        <v>0.05523853001597809</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18082,7 +17844,7 @@
         <v>30417.059602649006</v>
       </c>
       <c r="G4" s="19">
-        <v>0.06888686131386862</v>
+        <v>0.06893403332572472</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18103,7 +17865,7 @@
         <v>24300.104529616725</v>
       </c>
       <c r="G5" s="19">
-        <v>0.06546532846715329</v>
+        <v>0.06551015749828806</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18124,7 +17886,7 @@
         <v>3980.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.3759124087591241</v>
+        <v>0.37616982424104084</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18145,7 +17907,7 @@
         <v>59707.73786407767</v>
       </c>
       <c r="G7" s="19">
-        <v>0.023494525547445255</v>
+        <v>0.023510614015065052</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18166,7 +17928,7 @@
         <v>8999.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.07937956204379562</v>
+        <v>0.07943391919653048</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18187,7 +17949,7 @@
         <v>29000.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.023722627737226276</v>
+        <v>0.02373887240356083</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18208,7 +17970,7 @@
         <v>74800.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.005702554744525547</v>
+        <v>0.0057064597123944304</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18229,7 +17991,7 @@
         <v>31879.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.009352189781021899</v>
+        <v>0.009358593928326865</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18239,18 +18001,18 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C12" s="13">
-        <v>819989</v>
+        <v>639992</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>74544.45454545454</v>
+        <v>79999.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.002509124087591241</v>
+        <v>0.0018260671079662178</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18271,7 +18033,7 @@
         <v>15129.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.007527372262773723</v>
+        <v>0.007532526820360649</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18292,7 +18054,7 @@
         <v>10480.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.010492700729927007</v>
+        <v>0.010499885870805753</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18313,7 +18075,7 @@
         <v>19800.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.004333941605839416</v>
+        <v>0.004336909381419767</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18334,7 +18096,7 @@
         <v>11661.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.006386861313868613</v>
+        <v>0.006391234877881762</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18355,7 +18117,7 @@
         <v>7160.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.006843065693430657</v>
+        <v>0.006847751654873316</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18376,7 +18138,7 @@
         <v>4500.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.006843065693430657</v>
+        <v>0.006847751654873316</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18397,7 +18159,7 @@
         <v>687.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.01072080291970803</v>
+        <v>0.01072814425930153</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
